--- a/카드_아키타입/00_기타(미분류).xlsx
+++ b/카드_아키타입/00_기타(미분류).xlsx
@@ -256,7 +256,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -281,7 +281,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -306,7 +306,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -881,7 +881,7 @@
       <row>53</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -1031,7 +1031,7 @@
       <row>67</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="34" name="Image 34" descr="Picture"/>
@@ -1181,7 +1181,7 @@
       <row>81</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="40" name="Image 40" descr="Picture"/>
@@ -1606,7 +1606,7 @@
       <row>122</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="57" name="Image 57" descr="Picture"/>

--- a/카드_아키타입/00_기타(미분류).xlsx
+++ b/카드_아키타입/00_기타(미분류).xlsx
@@ -453,8 +453,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>1085850</rowOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -478,8 +478,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>23</row>
-      <rowOff>1085850</rowOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -503,8 +503,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>23</row>
-      <rowOff>1085850</rowOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -528,8 +528,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>23</row>
-      <rowOff>1085850</rowOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -553,8 +553,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>23</row>
-      <rowOff>1085850</rowOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -578,8 +578,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
-      <rowOff>2171700</rowOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -603,7 +603,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -628,7 +628,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>40</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="733425"/>
@@ -653,7 +653,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>40</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="923925"/>
@@ -678,7 +678,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>40</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="923925"/>
@@ -703,7 +703,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>40</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="923925"/>
@@ -728,8 +728,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>1085850</rowOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="923925"/>
     <pic>
@@ -753,8 +753,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>40</row>
-      <rowOff>1085850</rowOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="923925"/>
     <pic>
@@ -778,8 +778,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>40</row>
-      <rowOff>1085850</rowOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="923925"/>
     <pic>
@@ -803,8 +803,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>40</row>
-      <rowOff>1085850</rowOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="923925"/>
     <pic>
@@ -828,8 +828,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>40</row>
-      <rowOff>1085850</rowOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="923925"/>
     <pic>
@@ -853,7 +853,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -878,7 +878,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>53</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="781050"/>
@@ -903,7 +903,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>53</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -928,7 +928,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>53</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -953,7 +953,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>53</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -978,8 +978,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>53</row>
-      <rowOff>1085850</rowOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1003,7 +1003,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1028,7 +1028,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>67</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="781050"/>
@@ -1053,7 +1053,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>67</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1078,7 +1078,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>67</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1103,7 +1103,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>67</row>
+      <row>71</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1128,8 +1128,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
-      <rowOff>1085850</rowOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1153,7 +1153,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1178,7 +1178,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>81</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="781050"/>
@@ -1203,7 +1203,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>81</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1228,7 +1228,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>81</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1253,7 +1253,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>81</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1278,8 +1278,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>81</row>
-      <rowOff>1085850</rowOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1303,7 +1303,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1328,7 +1328,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>92</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1353,7 +1353,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>92</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="609600"/>
@@ -1378,7 +1378,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>92</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1403,7 +1403,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>92</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1428,8 +1428,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
-      <rowOff>1085850</rowOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1453,8 +1453,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>92</row>
-      <rowOff>1085850</rowOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1478,8 +1478,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>92</row>
-      <rowOff>1085850</rowOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1503,8 +1503,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>92</row>
-      <rowOff>1085850</rowOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1528,8 +1528,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>92</row>
-      <rowOff>1085850</rowOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1553,8 +1553,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
-      <rowOff>2171700</rowOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1578,7 +1578,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="676275" cy="1047750"/>
@@ -1603,7 +1603,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>122</row>
+      <row>132</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="781050"/>
@@ -1628,7 +1628,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>122</row>
+      <row>132</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="657225"/>
@@ -1653,7 +1653,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>122</row>
+      <row>132</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="276225"/>
@@ -1664,281 +1664,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId59"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId62"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>133</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>2171700</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId70"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1959,11 +1684,11 @@
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId71"/>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1981,14 +1706,14 @@
       <row>145</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="942975" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId72"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2006,14 +1731,14 @@
       <row>145</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="285750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId73"/>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2031,14 +1756,14 @@
       <row>145</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1000125" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId74"/>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2056,9 +1781,284 @@
       <row>145</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>147</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="942975" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="285750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1000125" cy="1047750"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="75" name="Image 75" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -2078,8 +2078,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>145</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -2103,8 +2103,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>145</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -2128,8 +2128,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>145</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -2153,8 +2153,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>145</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -2466,7 +2466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>베이킹 파우더 / (소다)</t>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="D3" s="4" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>레몬 EO 또는 / 오렌지EO</t>
@@ -2557,7 +2557,7 @@
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
     </row>
-    <row r="6" ht="300" customHeight="1">
+    <row r="6" ht="320" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>베이킹 소다는
@@ -2593,7 +2593,7 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>1. 지퍼백이나 비닐봉지에 베이킹 소다를 계량하세요.
@@ -2646,7 +2646,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="16" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D14" s="8" t="n"/>
     </row>
-    <row r="15" ht="45" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>멘톨</t>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D15" s="8" t="n"/>
     </row>
-    <row r="16" ht="45" customHeight="1">
+    <row r="16" ht="48" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>자운고 인퓨즈오일</t>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D16" s="8" t="n"/>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="48" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
@@ -2754,7 +2754,7 @@
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
     </row>
-    <row r="20" ht="165" customHeight="1">
+    <row r="20" ht="176" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>--&gt;
@@ -2784,7 +2784,7 @@
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
     </row>
-    <row r="22" ht="120" customHeight="1">
+    <row r="22" ht="128" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
           <t>1. 종이에 멘톨을 계량하세요.
@@ -2811,221 +2811,233 @@
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
     </row>
-    <row r="24" ht="256.5" customHeight="1">
+    <row r="24" ht="85.5" customHeight="1">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="10" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
     </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="25" ht="85.5" customHeight="1">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="85.5" customHeight="1">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="6" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>로즈여성세정제    [워터류]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>순수한 물 , / 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>장미수</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>내추럴 셀룰로오즈</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="D32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>멘톨</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>0.1g</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>민트의 알콜성분.</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>유화제 멘톨이 워터와 섞이게</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>약쑥추출물</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>민감,진정</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="48" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>감초추출물</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>민감,진정</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="37" ht="48" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>헥산디올</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>보습, 균번식억제</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-    </row>
-    <row r="37" ht="165" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="176" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>로즈워터, 쑥, 감초 등 천연한방성분이
 함유 되어있고 젤타입니다.
@@ -3036,18 +3048,18 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-    </row>
-    <row r="39" ht="195" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="208" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>만들기과정
 1.워터, 하이셀을 계량합니다.
@@ -3064,150 +3076,151 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-    </row>
-    <row r="41" ht="171" customHeight="1"/>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43" ht="85.5" customHeight="1"/>
+    <row r="44" ht="85.5" customHeight="1"/>
+    <row r="45" ht="6" customHeight="1"/>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>로맨틱 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B43" s="2" t="n"/>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>곡물발효.</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출. 장미의 수용성성분다량</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑워터</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>로즈제라늄</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>30방울</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>피지균형, 호르몬균형</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>일랑일랑에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-    </row>
-    <row r="50" ht="225" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+    </row>
+    <row r="53" ht="240" customHeight="1">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -3225,22 +3238,22 @@
 '방향제'로도요^^</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-    </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-    </row>
-    <row r="52" ht="75" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+    </row>
+    <row r="55" ht="80" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95와
@@ -3249,181 +3262,187 @@
 4. 흔들어주면 완성.</t>
         </is>
       </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-    </row>
-    <row r="53" ht="14" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-    </row>
-    <row r="54" ht="171" customHeight="1">
-      <c r="A54" s="10" t="n"/>
-      <c r="B54" s="10" t="n"/>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="10" t="n"/>
-    </row>
-    <row r="55" ht="6" customHeight="1"/>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+    </row>
+    <row r="57" ht="85.5" customHeight="1">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+    </row>
+    <row r="58" ht="85.5" customHeight="1">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+    </row>
+    <row r="59" ht="6" customHeight="1"/>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="1" t="inlineStr">
         <is>
           <t>리프레쉬 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>곡물발효</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>편백워터</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>피톤치드 함유, 편백잎을 수증기추출</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>로즈마리워터</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>라임에센셜오일</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>라임껍질오일, 기분전환</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>버가못, 레몬EO</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>스피아민트에센셜오일</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="14" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B63" s="6" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-    </row>
-    <row r="64" ht="165" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="6" t="n"/>
+      <c r="D67" s="6" t="n"/>
+    </row>
+    <row r="68" ht="176" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -3439,18 +3458,18 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6" t="n"/>
-    </row>
-    <row r="66" ht="75" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+    </row>
+    <row r="70" ht="80" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95와
@@ -3460,172 +3479,173 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-    </row>
-    <row r="68" ht="171" customHeight="1"/>
-    <row r="69" ht="6" customHeight="1"/>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+    </row>
+    <row r="72" ht="85.5" customHeight="1"/>
+    <row r="73" ht="85.5" customHeight="1"/>
+    <row r="74" ht="6" customHeight="1"/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="1" t="inlineStr">
         <is>
           <t>릴렉스 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>곡물발효</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>진정, 라벤더꽃을 수증기증류추출</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>어성초우린물, 캐모마일워터 등</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
         <is>
           <t>오렌지에센셜오일</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>오렌지껍질압착, 달콤한 향</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>버가못, 레몬EO</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>라벤더꽃에서 추출,진정, 불면증 도움</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="14" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="D77" s="6" t="n"/>
-    </row>
-    <row r="78" ht="195" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+    </row>
+    <row r="83" ht="208" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -3642,22 +3662,22 @@
 '방향제'로도요^^</t>
         </is>
       </c>
-      <c r="B78" s="10" t="n"/>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="10" t="n"/>
-    </row>
-    <row r="79" ht="14" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n"/>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="6" t="n"/>
-      <c r="D79" s="6" t="n"/>
-    </row>
-    <row r="80" ht="75" customHeight="1">
-      <c r="A80" s="9" t="inlineStr">
+      <c r="B84" s="6" t="n"/>
+      <c r="C84" s="6" t="n"/>
+      <c r="D84" s="6" t="n"/>
+    </row>
+    <row r="85" ht="80" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95
@@ -3666,107 +3686,113 @@
 4. 흔들어주면 완성.</t>
         </is>
       </c>
-      <c r="B80" s="10" t="n"/>
-      <c r="C80" s="10" t="n"/>
-      <c r="D80" s="10" t="n"/>
-    </row>
-    <row r="81" ht="14" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="10" t="n"/>
+      <c r="D85" s="10" t="n"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="6" t="n"/>
-      <c r="D81" s="6" t="n"/>
-    </row>
-    <row r="82" ht="171" customHeight="1">
-      <c r="A82" s="10" t="n"/>
-      <c r="B82" s="10" t="n"/>
-      <c r="C82" s="10" t="n"/>
-      <c r="D82" s="10" t="n"/>
-    </row>
-    <row r="83" ht="6" customHeight="1"/>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="1" t="inlineStr">
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="6" t="n"/>
+      <c r="D86" s="6" t="n"/>
+    </row>
+    <row r="87" ht="85.5" customHeight="1">
+      <c r="A87" s="10" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="10" t="n"/>
+      <c r="D87" s="10" t="n"/>
+    </row>
+    <row r="88" ht="85.5" customHeight="1">
+      <c r="A88" s="10" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="10" t="n"/>
+    </row>
+    <row r="89" ht="6" customHeight="1"/>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>계피 진드기ZERO 스프레이    [100ml / 용기기준]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B84" s="2" t="n"/>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n"/>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="255" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
+    <row r="92" ht="272" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>계피에센셜오일 / (시나몬오일)</t>
         </is>
       </c>
-      <c r="B86" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>40방울 / (2ml)</t>
         </is>
       </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>녹나무과 식물이고 나무껍질을 주로 활용. / 중국,스리랑카, 인도, 동남아시아가 원산지죠. / 계피 나무껍질 향은 상당히 강하고 달콤하면서 맵습니다. / 계피의 나무껍질을 수증기증류법으로 추출하면몇십배 농축된 계피오일을 추출할 수 있습니다.주성분이 시남알데히드(cinnamaldehyde)로 80~90%을 차지. 알데하이드성분은 벌레퇴치,항진균효과가 탁월. 계피오일은 예로부터 강력한 살균, 항진균, 방충, 소화촉진 마취, 방부효과가 있어 활용한 예가 많습니다. / 단, 고농축인 계피오일은 피부자극이 있기 때문에 피부에 직접 사용하는 것은 피해주세요. / 임산부도 사용을 금합니다.</t>
         </is>
       </c>
-      <c r="D86" s="4" t="n"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="D92" s="4" t="n"/>
+    </row>
+    <row r="93" ht="32" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>보존제, 희석용매, 오일이 분리되지 않고 잘 분산이 되도록 함.</t>
         </is>
       </c>
-      <c r="D87" s="4" t="n"/>
-    </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="D93" s="4" t="n"/>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="6" t="n"/>
-      <c r="D88" s="6" t="n"/>
-    </row>
-    <row r="89" ht="600" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+    </row>
+    <row r="95" ht="384" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>큰아이 다은이는 코막힘, 콧물 증상 때문에 병원에 한번씩 가면
 담당 의사선생님이 감기약보다 알르레기 비염약도 항상 처방을 해주셨어요.
@@ -3791,8 +3817,14 @@
 이런 것들이 부족할 때는 식물의 꽃가루나 각종 먼지의 조각들도 먹고 자기의 배설물과
 동료의 시체까지 먹어치우는 왕성한 식욕을 가졌습니다.^^;;
 집먼지진드기는 자신의 몸무게에 200배 달하는 배설물을 매일 방출합니다.
-( 실제 배설물이 알러지를 유발합니다.)집먼지진드기는 수명이 6주이고
-어미진드기는 3주마다 새진드기를 낳습니다. 어마어한 놈입니다.ㅠㅠ
+( 실제 배설물이 알러지를 유발합니다.)집먼지진드기는 수명이 6주이고</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="384" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>어미진드기는 3주마다 새진드기를 낳습니다. 어마어한 놈입니다.ㅠㅠ
 여러 매체에서 소개된 각종 알레르기 질환의 주범인
 집먼지진드기 제거에 효과적인 방법 6가지
 (요녀석~~! 죽었어^^)
@@ -3815,8 +3847,14 @@
 6.계피스프레이 만들어 활용하기!
 위기탈출 넘버원 등에서 집먼지진드기제거에 확실한 효과가 입증된 계피스프레이.
 강력한 진균,방충효과가 있는 핵심재료인 계피오일은
-녹나무과 식물이고 나무껍질을 주로 사용합니다.
-중국, 스리랑카, 인도, 동남아시아가 원산지죠.
+녹나무과 식물이고 나무껍질을 주로 사용합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="336" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>중국, 스리랑카, 인도, 동남아시아가 원산지죠.
 계피 나무껍질,잎의 향은 상당히 강하고 달콤하면서 맵습니다.
 계피의 나무껍질,잎을 수증기증류법으로 추출하면
 몇십배 농축된 계피오일을 추출할 수 있습니다.
@@ -3840,18 +3878,18 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="14" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6" t="n"/>
-    </row>
-    <row r="91" ht="135" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+    </row>
+    <row r="99" ht="144" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>계피스프레이 초정밀 만들기과정
 [100ml 용기기준]
@@ -3865,106 +3903,108 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="14" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-    </row>
-    <row r="93" ht="256.5" customHeight="1"/>
-    <row r="94" ht="6" customHeight="1"/>
-    <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="1" t="inlineStr">
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+    </row>
+    <row r="101" ht="85.5" customHeight="1"/>
+    <row r="102" ht="85.5" customHeight="1"/>
+    <row r="103" ht="85.5" customHeight="1"/>
+    <row r="104" ht="6" customHeight="1"/>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="1" t="inlineStr">
         <is>
           <t>어성초팅크처    ↗ 원본</t>
         </is>
       </c>
-      <c r="B95" s="2" t="n"/>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n"/>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="45" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
+    <row r="107" ht="48" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>7.41%</t>
         </is>
       </c>
-      <c r="C97" s="8" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>어성초 추출, 물고기 비린내가 난다하여 어성초, 각종 피부트러블, 피부 개선에 사용</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>녹차, 병풀, 알란토인,카렌듈라추출물, 유기농 프레쉬 5솔루션 등</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="8" t="inlineStr">
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>에탄올(변성)</t>
         </is>
       </c>
-      <c r="B98" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>92.59%</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>가용화제, / 물에 오일이 골고루 분산</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-    </row>
-    <row r="100" ht="135" customHeight="1">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="B109" s="6" t="n"/>
+      <c r="C109" s="6" t="n"/>
+      <c r="D109" s="6" t="n"/>
+    </row>
+    <row r="110" ht="144" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>◎ 이렇게 잘 만들어진 어성초팅크처
 1. 보관기간은 알콜이기 때문에 1년이상 보관하실 수 있구요.
@@ -3973,301 +4013,301 @@
 4. 더 진하게 만들고 싶다면.. 담그고 2주 후 어성초건초를 빼내고 새로운 어성초 40g정도를 넣어주세요. 또 2주나 한달을 숙성하시면 되요. 그러면 한번한 것보다는 팅크처를 진하게 만들 수 있어요. ^^</t>
         </is>
       </c>
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="10" t="n"/>
-      <c r="D100" s="10" t="n"/>
-    </row>
-    <row r="101" ht="14" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="B110" s="10" t="n"/>
+      <c r="C110" s="10" t="n"/>
+      <c r="D110" s="10" t="n"/>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B101" s="6" t="n"/>
-      <c r="C101" s="6" t="n"/>
-      <c r="D101" s="6" t="n"/>
-    </row>
-    <row r="102" ht="45" customHeight="1">
-      <c r="A102" s="9" t="inlineStr">
+      <c r="B111" s="6" t="n"/>
+      <c r="C111" s="6" t="n"/>
+      <c r="D111" s="6" t="n"/>
+    </row>
+    <row r="112" ht="48" customHeight="1">
+      <c r="A112" s="9" t="inlineStr">
         <is>
           <t>1. 어성초건초 40g을 병에 눌러 담는다.
 2. 병에 식물성에탄올(순수발효주정) 500g 넣는다.
 3. 2주나 한달정도 숙성하면 완성!(그늘지고 서늘한 곳에서 보관요)</t>
         </is>
       </c>
-      <c r="B102" s="10" t="n"/>
-      <c r="C102" s="10" t="n"/>
-      <c r="D102" s="10" t="n"/>
-    </row>
-    <row r="103" ht="14" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+      <c r="B112" s="10" t="n"/>
+      <c r="C112" s="10" t="n"/>
+      <c r="D112" s="10" t="n"/>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B103" s="6" t="n"/>
-      <c r="C103" s="6" t="n"/>
-      <c r="D103" s="6" t="n"/>
-    </row>
-    <row r="104" ht="85.5" customHeight="1">
-      <c r="A104" s="10" t="n"/>
-      <c r="B104" s="10" t="n"/>
-      <c r="C104" s="10" t="n"/>
-      <c r="D104" s="10" t="n"/>
-    </row>
-    <row r="105" ht="6" customHeight="1"/>
-    <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="1" t="inlineStr">
+      <c r="B113" s="6" t="n"/>
+      <c r="C113" s="6" t="n"/>
+      <c r="D113" s="6" t="n"/>
+    </row>
+    <row r="114" ht="85.5" customHeight="1">
+      <c r="A114" s="10" t="n"/>
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="10" t="n"/>
+      <c r="D114" s="10" t="n"/>
+    </row>
+    <row r="115" ht="6" customHeight="1"/>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="1" t="inlineStr">
         <is>
           <t>아로마 물파스    ↗ 원본</t>
         </is>
       </c>
-      <c r="B106" s="2" t="n"/>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>위치헤이즐워터</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="D118" s="4" t="inlineStr">
         <is>
           <t>편백워터</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>알로에겔(국내거제산)</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>수분공급,진정</t>
         </is>
       </c>
-      <c r="D109" s="4" t="n"/>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="4" t="inlineStr">
+      <c r="D119" s="4" t="n"/>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>점증제</t>
         </is>
       </c>
-      <c r="D110" s="4" t="n"/>
-    </row>
-    <row r="111" ht="60" customHeight="1">
-      <c r="A111" s="4" t="inlineStr">
+      <c r="D120" s="4" t="n"/>
+    </row>
+    <row r="121" ht="64" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>멘톨</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C111" s="4" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>박하뇌라고도하고 알콜성분, 박하의 잎, 꽃에서 수증기 증류하여 얻어진다. 물에 녹지않고 진통제 가려움증을 멈추는데 사용</t>
         </is>
       </c>
-      <c r="D111" s="4" t="n"/>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="D121" s="4" t="n"/>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>식물성에탄올</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>16g</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>곡물발효주정, 소주원액, 소독</t>
         </is>
       </c>
-      <c r="D112" s="4" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="4" t="inlineStr">
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>인플라신</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C113" s="4" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>항염</t>
         </is>
       </c>
-      <c r="D113" s="4" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>알란토인</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="4" t="inlineStr">
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>가용화제, 워터와 오일들 분리저지</t>
         </is>
       </c>
-      <c r="D114" s="4" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="4" t="inlineStr">
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C115" s="4" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="D115" s="4" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>캐모마일로먼,저먼</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="D116" s="4" t="inlineStr">
+      <c r="D126" s="4" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="4" t="inlineStr">
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>로즈마리에센셜오일</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C117" s="4" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>혈액순환</t>
         </is>
       </c>
-      <c r="D117" s="4" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr">
         <is>
           <t>페파민트 등</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="14" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6" t="n"/>
-    </row>
-    <row r="119" ht="75" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="6" t="n"/>
+    </row>
+    <row r="129" ht="80" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>[ 레시피 재료 ]
 ① 위치헤이즐워터 50g, 천연알로에베라원액 20g, 하이셀 1g
@@ -4276,18 +4316,18 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="5" t="inlineStr">
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B120" s="6" t="n"/>
-      <c r="C120" s="6" t="n"/>
-      <c r="D120" s="6" t="n"/>
-    </row>
-    <row r="121" ht="120" customHeight="1">
-      <c r="A121" s="7" t="inlineStr">
+      <c r="B130" s="6" t="n"/>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="6" t="n"/>
+    </row>
+    <row r="131" ht="128" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 알로에겔, 위치헤이즐워터, 하이셀을 계량한다.
@@ -4300,102 +4340,102 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="14" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B122" s="6" t="n"/>
-      <c r="C122" s="6" t="n"/>
-      <c r="D122" s="6" t="n"/>
-    </row>
-    <row r="123" ht="85.5" customHeight="1"/>
-    <row r="124" ht="6" customHeight="1"/>
-    <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="1" t="inlineStr">
+      <c r="B132" s="6" t="n"/>
+      <c r="C132" s="6" t="n"/>
+      <c r="D132" s="6" t="n"/>
+    </row>
+    <row r="133" ht="85.5" customHeight="1"/>
+    <row r="134" ht="6" customHeight="1"/>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="1" t="inlineStr">
         <is>
           <t>데일리 스마트폰 소독제    [100ml기준]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B125" s="2" t="n"/>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n"/>
-    </row>
-    <row r="126" ht="15" customHeight="1">
-      <c r="A126" s="3" t="inlineStr">
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n"/>
+    </row>
+    <row r="136" ht="15" customHeight="1">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="30" customHeight="1">
-      <c r="A127" s="8" t="inlineStr">
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
         </is>
       </c>
-      <c r="B127" s="8" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C127" s="8" t="inlineStr">
+      <c r="C137" s="8" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼향, 기분전환, / 항균^^</t>
         </is>
       </c>
-      <c r="D127" s="8" t="inlineStr">
+      <c r="D137" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="8" t="inlineStr">
+    <row r="138" ht="32" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B128" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>100ml(87g)</t>
         </is>
       </c>
-      <c r="C128" s="8" t="inlineStr">
+      <c r="C138" s="8" t="inlineStr">
         <is>
           <t>소독,살균</t>
         </is>
       </c>
-      <c r="D128" s="8" t="n"/>
-    </row>
-    <row r="129" ht="14" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
+      <c r="D138" s="8" t="n"/>
+    </row>
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B129" s="6" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
-    </row>
-    <row r="130" ht="600" customHeight="1">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+    </row>
+    <row r="140" ht="384" customHeight="1">
+      <c r="A140" s="9" t="inlineStr">
         <is>
           <t>매일 사용하는 스마트폰이 화장실변기보다 세균과 바이러스가 10배이상 많이 검출된다는
 뉴스를 접한 적이 있어요. (뜨아~~)
@@ -4420,8 +4460,17 @@
 그런데 100% 에탄올은 단백질을 응고시키는 능력이
 너무 탁월해 세균 표면의 단백질을 한꺼번에 응고시켜버리기 때문에
 세균 표면에 단단한 막이 생성됩니다.
-이 막은 에탄올이 세균 내부로 침투하는 것을 막습니다.
-따라서 살균작용이 효과적으로 일어나게 하려면 순수 에탄올에 물을 섞어야 한답니다.
+이 막은 에탄올이 세균 내부로 침투하는 것을 막습니다.</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="n"/>
+      <c r="C140" s="10" t="n"/>
+      <c r="D140" s="10" t="n"/>
+    </row>
+    <row r="141" ht="384" customHeight="1">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
+          <t>따라서 살균작용이 효과적으로 일어나게 하려면 순수 에탄올에 물을 섞어야 한답니다.
 세균 표면의 막을 한꺼번에 응고시키는 것을 막아고
 에탄올 분자가 세균의 체내로 뚫고 들어갈 수 있게 하는 것입니다.
 에탄올은 70%정도가 가장 강한 살균력을 나타내며,
@@ -4444,27 +4493,36 @@
 스마트폰 소독제는
 마우스나 키보드, 리모컨 소독에 사용할 수 있습니다.
 또 화장실 손잡이도 소독하세요.
-방법은 같습니다.
-면거즈나 (키친타올이나) 티슈에 촉촉할 정도로 적셔서
+방법은 같습니다.</t>
+        </is>
+      </c>
+      <c r="B141" s="10" t="n"/>
+      <c r="C141" s="10" t="n"/>
+      <c r="D141" s="10" t="n"/>
+    </row>
+    <row r="142" ht="32" customHeight="1">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>면거즈나 (키친타올이나) 티슈에 촉촉할 정도로 적셔서
 닦아주세요.</t>
         </is>
       </c>
-      <c r="B130" s="10" t="n"/>
-      <c r="C130" s="10" t="n"/>
-      <c r="D130" s="10" t="n"/>
-    </row>
-    <row r="131" ht="14" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
+      <c r="B142" s="10" t="n"/>
+      <c r="C142" s="10" t="n"/>
+      <c r="D142" s="10" t="n"/>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B131" s="6" t="n"/>
-      <c r="C131" s="6" t="n"/>
-      <c r="D131" s="6" t="n"/>
-    </row>
-    <row r="132" ht="195" customHeight="1">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="B143" s="6" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+    </row>
+    <row r="144" ht="208" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.용기에 에센셜오일을 20방울 떨어뜨려주세요. (에센셜오일을 넣지 않는다면 생략 가능)
@@ -4480,133 +4538,145 @@
 오랜만에 닦으니 어찌나 지저분한지.. 상큼한 레몬 잔향이 기분좋게 만드네요.</t>
         </is>
       </c>
-      <c r="B132" s="10" t="n"/>
-      <c r="C132" s="10" t="n"/>
-      <c r="D132" s="10" t="n"/>
-    </row>
-    <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="10" t="n"/>
+    </row>
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B133" s="6" t="n"/>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6" t="n"/>
-    </row>
-    <row r="134" ht="256.5" customHeight="1">
-      <c r="A134" s="10" t="n"/>
-      <c r="B134" s="10" t="n"/>
-      <c r="C134" s="10" t="n"/>
-      <c r="D134" s="10" t="n"/>
-    </row>
-    <row r="135" ht="6" customHeight="1"/>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="1" t="inlineStr">
+      <c r="B145" s="6" t="n"/>
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+    </row>
+    <row r="146" ht="85.5" customHeight="1">
+      <c r="A146" s="10" t="n"/>
+      <c r="B146" s="10" t="n"/>
+      <c r="C146" s="10" t="n"/>
+      <c r="D146" s="10" t="n"/>
+    </row>
+    <row r="147" ht="85.5" customHeight="1">
+      <c r="A147" s="10" t="n"/>
+      <c r="B147" s="10" t="n"/>
+      <c r="C147" s="10" t="n"/>
+      <c r="D147" s="10" t="n"/>
+    </row>
+    <row r="148" ht="85.5" customHeight="1">
+      <c r="A148" s="10" t="n"/>
+      <c r="B148" s="10" t="n"/>
+      <c r="C148" s="10" t="n"/>
+      <c r="D148" s="10" t="n"/>
+    </row>
+    <row r="149" ht="6" customHeight="1"/>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="1" t="inlineStr">
         <is>
           <t>아로마 손소독제스프레이    ↗ 원본</t>
         </is>
       </c>
-      <c r="B136" s="2" t="n"/>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n"/>
-    </row>
-    <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+    </row>
+    <row r="151" ht="15" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="60" customHeight="1">
-      <c r="A138" s="4" t="inlineStr">
+    <row r="152" ht="64" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>465ml</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>곡물 발효 , / 소독효과가 제일 좋은 70% 알코올함량, / 에센셜오일 분산, 방향용으로 사용시 / 공기정화, 소독효과.</t>
         </is>
       </c>
-      <c r="D138" s="4" t="n"/>
-    </row>
-    <row r="139" ht="30" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
+      <c r="D152" s="4" t="n"/>
+    </row>
+    <row r="153" ht="48" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>22.5g</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>손 보습제, 향과 알코올이 오랫동안 머물 수 / 있도록 고착제 역할을 함.</t>
         </is>
       </c>
-      <c r="D139" s="4" t="inlineStr">
+      <c r="D153" s="4" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="30" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+    <row r="154" ht="32" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>(레몬) 에센셜오일</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>2~5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 / 천연오일. 원하는 향.</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D154" s="4" t="inlineStr">
         <is>
           <t>클린코튼, 그린티시트러스, 체리블라썸 향 등</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="14" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B141" s="6" t="n"/>
-      <c r="C141" s="6" t="n"/>
-      <c r="D141" s="6" t="n"/>
-    </row>
-    <row r="142" ht="465" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
+      <c r="B155" s="6" t="n"/>
+      <c r="C155" s="6" t="n"/>
+      <c r="D155" s="6" t="n"/>
+    </row>
+    <row r="156" ht="384" customHeight="1">
+      <c r="A156" s="7" t="inlineStr">
         <is>
           <t>2009년 신종 플루 때 안내해드린 레시피입니다.
 이번 메르스, 신종 플루 때처럼 사람들을 불안하게 하네요.
@@ -4630,8 +4700,14 @@
 따라서 살균작용이 효과적으로 일어나게 하려면 순수 에탄올에 물을 섞어야 합니다.
 세균 표면의 막을 한꺼번에 응고시키는 것을 막고
 에탄올 분자가 세균의 체내로 뚫고 들어갈 수 있게 하는 것입니다.
-에탄올은 70%정도가 가장 강한 살균력을 나타내며,
-60% 이하나, 80% 이상에서는 거의 살균력이 없습니다.
+에탄올은 70%정도가 가장 강한 살균력을 나타내며,</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="112" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>60% 이하나, 80% 이상에서는 거의 살균력이 없습니다.
 에탄올 80%이상에서 살균분무시 알콜성분이 빨리 공기 중에
 증발하여 지속적인 살균이 어렵기도 하답니다.
 이점 참고하세요.
@@ -4641,18 +4717,18 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="14" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B143" s="6" t="n"/>
-      <c r="C143" s="6" t="n"/>
-      <c r="D143" s="6" t="n"/>
-    </row>
-    <row r="144" ht="150" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
+      <c r="B158" s="6" t="n"/>
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="6" t="n"/>
+    </row>
+    <row r="159" ht="160" customHeight="1">
+      <c r="A159" s="7" t="inlineStr">
         <is>
           <t>초간단 만들기과정
 1. 아로마베이스70 속/겉뚜껑을 열고
@@ -4666,30 +4742,36 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="14" customHeight="1">
-      <c r="A145" s="5" t="inlineStr">
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B145" s="6" t="n"/>
-      <c r="C145" s="6" t="n"/>
-      <c r="D145" s="6" t="n"/>
-    </row>
-    <row r="146" ht="171" customHeight="1"/>
-    <row r="147" ht="6" customHeight="1"/>
+      <c r="B160" s="6" t="n"/>
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="6" t="n"/>
+    </row>
+    <row r="161" ht="85.5" customHeight="1"/>
+    <row r="162" ht="85.5" customHeight="1"/>
+    <row r="163" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="77">
+  <mergeCells count="93">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A150:D150"/>
     <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A159:D159"/>
+    <mergeCell ref="A97:D97"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A121:D121"/>
-    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A112:D112"/>
+    <mergeCell ref="A161:D161"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A114:D114"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A70:D70"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A7:D7"/>
@@ -4697,79 +4779,90 @@
     <mergeCell ref="A99:D99"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A141:D141"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A53:D53"/>
-    <mergeCell ref="A125:D125"/>
+    <mergeCell ref="A135:D135"/>
     <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A111:D111"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A142:D142"/>
-    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A98:D98"/>
     <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A162:D162"/>
+    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A90:D90"/>
-    <mergeCell ref="A136:D136"/>
+    <mergeCell ref="A105:D105"/>
     <mergeCell ref="A145:D145"/>
     <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="A71:D71"/>
     <mergeCell ref="A129:D129"/>
+    <mergeCell ref="A116:D116"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A91:D91"/>
     <mergeCell ref="A131:D131"/>
     <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A140:D140"/>
+    <mergeCell ref="A109:D109"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A155:D155"/>
     <mergeCell ref="A68:D68"/>
     <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A83:D83"/>
     <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A157:D157"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A94:D94"/>
     <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A87:D87"/>
     <mergeCell ref="A133:D133"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A120:D120"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A113:D113"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A106:D106"/>
     <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A147:D147"/>
     <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A156:D156"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A67:D67"/>
     <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A148:D148"/>
     <mergeCell ref="A82:D82"/>
-    <mergeCell ref="A123:D123"/>
     <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A110:D110"/>
     <mergeCell ref="A146:D146"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A119:D119"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A84:D84"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A158:D158"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A160:D160"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>

--- a/카드_아키타입/00_기타(미분류).xlsx
+++ b/카드_아키타입/00_기타(미분류).xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="6591300"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="6591300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="6591300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="8439150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>9</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="8439150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>9</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="8439150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>9</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="8439150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="10287000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>9</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="10287000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>9</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="10287000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="13589000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="13589000"/>
     <ext cx="1809750" cy="1266825"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="13589000"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>21</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="13589000"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="15436850"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="15436850"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="15436850"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>21</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="15436850"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>21</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="17284700"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>21</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="17284700"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="22618700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="22618700"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="22618700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>36</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="22618700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>36</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="24466550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>36</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="24466550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="28803600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="28803600"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="28803600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="28803600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="30651450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="30651450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="34582100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="34582100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="34582100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="34582100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="36429950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>59</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="36429950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>71</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="40767000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>71</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="40767000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>71</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="40767000"/>
     <ext cx="1809750" cy="1057275"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>71</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="40767000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>71</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="42614850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>71</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="42614850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>71</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="42614850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>71</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="42614850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>71</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="44462700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>71</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="44462700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>71</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="44462700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>82</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="61379100"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="65735200"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="65735200"/>
     <ext cx="1809750" cy="1133475"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="65735200"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="72123300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="72123300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="72123300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>108</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="72123300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>108</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73971150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>108</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="73971150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>108</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="73971150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>108</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="73971150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>108</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="75819000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>108</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="75819000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>108</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="75819000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>119</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="86639400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>119</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="86639400"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>119</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="86639400"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>119</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="86639400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>119</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="88487250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>119</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="88487250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>119</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="88487250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>119</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="88487250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>119</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="90335100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2173,7 +1778,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/00_기타(미분류).xlsx
+++ b/카드_아키타입/00_기타(미분류).xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="6591300"/>
+    <pos x="7391400" y="6591300"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="6591300"/>
+    <pos x="9239250" y="6591300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="6591300"/>
+    <pos x="11087100" y="6591300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="6591300"/>
+    <pos x="12934950" y="6591300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="8439150"/>
+    <pos x="7391400" y="8439150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="8439150"/>
+    <pos x="9239250" y="8439150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="8439150"/>
+    <pos x="11087100" y="8439150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="8439150"/>
+    <pos x="12934950" y="8439150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="10287000"/>
+    <pos x="7391400" y="10287000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="10287000"/>
+    <pos x="9239250" y="10287000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="10287000"/>
+    <pos x="11087100" y="10287000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="13589000"/>
+    <pos x="7391400" y="13589000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="13589000"/>
+    <pos x="9239250" y="13589000"/>
     <ext cx="1809750" cy="1266825"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="13589000"/>
+    <pos x="11087100" y="13589000"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="13589000"/>
+    <pos x="12934950" y="13589000"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="15436850"/>
+    <pos x="7391400" y="15436850"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="15436850"/>
+    <pos x="9239250" y="15436850"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="15436850"/>
+    <pos x="11087100" y="15436850"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="15436850"/>
+    <pos x="12934950" y="15436850"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="17284700"/>
+    <pos x="7391400" y="17284700"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="17284700"/>
+    <pos x="9239250" y="17284700"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="22618700"/>
+    <pos x="7391400" y="22618700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="22618700"/>
+    <pos x="9239250" y="22618700"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="22618700"/>
+    <pos x="11087100" y="22618700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="22618700"/>
+    <pos x="12934950" y="22618700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="24466550"/>
+    <pos x="7391400" y="24466550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="24466550"/>
+    <pos x="9239250" y="24466550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="28803600"/>
+    <pos x="7391400" y="28803600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="28803600"/>
+    <pos x="9239250" y="28803600"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="28803600"/>
+    <pos x="11087100" y="28803600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="28803600"/>
+    <pos x="12934950" y="28803600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="30651450"/>
+    <pos x="7391400" y="30651450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="30651450"/>
+    <pos x="9239250" y="30651450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="34582100"/>
+    <pos x="7391400" y="34582100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="34582100"/>
+    <pos x="9239250" y="34582100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="34582100"/>
+    <pos x="11087100" y="34582100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="34582100"/>
+    <pos x="12934950" y="34582100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="36429950"/>
+    <pos x="7391400" y="36429950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="36429950"/>
+    <pos x="9239250" y="36429950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="40767000"/>
+    <pos x="7391400" y="40767000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="40767000"/>
+    <pos x="9239250" y="40767000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="40767000"/>
+    <pos x="11087100" y="40767000"/>
     <ext cx="1809750" cy="1057275"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="40767000"/>
+    <pos x="12934950" y="40767000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="42614850"/>
+    <pos x="7391400" y="42614850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="42614850"/>
+    <pos x="9239250" y="42614850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="42614850"/>
+    <pos x="11087100" y="42614850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="42614850"/>
+    <pos x="12934950" y="42614850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="44462700"/>
+    <pos x="7391400" y="44462700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="44462700"/>
+    <pos x="9239250" y="44462700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="44462700"/>
+    <pos x="11087100" y="44462700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="61379100"/>
+    <pos x="7391400" y="61379100"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="65735200"/>
+    <pos x="7391400" y="65735200"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="65735200"/>
+    <pos x="9239250" y="65735200"/>
     <ext cx="1809750" cy="1133475"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="65735200"/>
+    <pos x="11087100" y="65735200"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="72123300"/>
+    <pos x="7391400" y="72123300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="72123300"/>
+    <pos x="9239250" y="72123300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="72123300"/>
+    <pos x="11087100" y="72123300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="72123300"/>
+    <pos x="12934950" y="72123300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73971150"/>
+    <pos x="7391400" y="73971150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="73971150"/>
+    <pos x="9239250" y="73971150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="73971150"/>
+    <pos x="11087100" y="73971150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="73971150"/>
+    <pos x="12934950" y="73971150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="75819000"/>
+    <pos x="7391400" y="75819000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="75819000"/>
+    <pos x="9239250" y="75819000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="75819000"/>
+    <pos x="11087100" y="75819000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="86639400"/>
+    <pos x="7391400" y="86639400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="86639400"/>
+    <pos x="9239250" y="86639400"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="86639400"/>
+    <pos x="11087100" y="86639400"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="86639400"/>
+    <pos x="12934950" y="86639400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="88487250"/>
+    <pos x="7391400" y="88487250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="88487250"/>
+    <pos x="9239250" y="88487250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="88487250"/>
+    <pos x="11087100" y="88487250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="88487250"/>
+    <pos x="12934950" y="88487250"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="90335100"/>
+    <pos x="7391400" y="90335100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2078,7 +2078,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/00_기타(미분류).xlsx
+++ b/카드_아키타입/00_기타(미분류).xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B5900"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="003A3A3A"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,16 +46,31 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002A4A6B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="0055606E"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEFBE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6DC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -60,7 +84,57 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBD9E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F7FAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD9F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9F0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8F5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFF3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6DAF5"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,32 +169,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -200,7 +319,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7391400" y="0"/>
+    <pos x="7848600" y="1092200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -220,7 +339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="0"/>
+    <pos x="9696450" y="1092200"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -240,7 +359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="0"/>
+    <pos x="11544300" y="1092200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="0"/>
+    <pos x="13392150" y="1092200"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="1847850"/>
+    <pos x="7848600" y="2940050"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="6591300"/>
+    <pos x="7848600" y="7861300"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -320,7 +439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="6591300"/>
+    <pos x="9696450" y="7861300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -340,7 +459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="6591300"/>
+    <pos x="11544300" y="7861300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="6591300"/>
+    <pos x="13392150" y="7861300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -380,7 +499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="8439150"/>
+    <pos x="7848600" y="9709150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -400,7 +519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="8439150"/>
+    <pos x="9696450" y="9709150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -420,7 +539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="8439150"/>
+    <pos x="11544300" y="9709150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -440,7 +559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="8439150"/>
+    <pos x="13392150" y="9709150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -460,7 +579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="10287000"/>
+    <pos x="7848600" y="11557000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -480,7 +599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="10287000"/>
+    <pos x="9696450" y="11557000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -500,7 +619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="10287000"/>
+    <pos x="11544300" y="11557000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -520,7 +639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="13589000"/>
+    <pos x="7848600" y="15443200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -540,7 +659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="13589000"/>
+    <pos x="9696450" y="15443200"/>
     <ext cx="1809750" cy="1266825"/>
     <pic>
       <nvPicPr>
@@ -560,7 +679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="13589000"/>
+    <pos x="11544300" y="15443200"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -580,7 +699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="13589000"/>
+    <pos x="13392150" y="15443200"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -600,7 +719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="15436850"/>
+    <pos x="7848600" y="17291050"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -620,7 +739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="15436850"/>
+    <pos x="9696450" y="17291050"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -640,7 +759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="15436850"/>
+    <pos x="11544300" y="17291050"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -660,7 +779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="15436850"/>
+    <pos x="13392150" y="17291050"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -680,7 +799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="17284700"/>
+    <pos x="7848600" y="19138900"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -700,7 +819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="17284700"/>
+    <pos x="9696450" y="19138900"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -720,7 +839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="22618700"/>
+    <pos x="7848600" y="25260300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -740,7 +859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="22618700"/>
+    <pos x="9696450" y="25260300"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -760,7 +879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="22618700"/>
+    <pos x="11544300" y="25260300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -780,7 +899,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="22618700"/>
+    <pos x="13392150" y="25260300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -800,7 +919,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="24466550"/>
+    <pos x="7848600" y="27108150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -820,7 +939,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="24466550"/>
+    <pos x="9696450" y="27108150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -840,7 +959,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="28803600"/>
+    <pos x="7848600" y="31826200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -860,7 +979,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="28803600"/>
+    <pos x="9696450" y="31826200"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -880,7 +999,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="28803600"/>
+    <pos x="11544300" y="31826200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -900,7 +1019,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="28803600"/>
+    <pos x="13392150" y="31826200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -920,7 +1039,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="30651450"/>
+    <pos x="7848600" y="33674050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -940,7 +1059,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="30651450"/>
+    <pos x="9696450" y="33674050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -960,7 +1079,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="34582100"/>
+    <pos x="7848600" y="37985700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -980,7 +1099,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="34582100"/>
+    <pos x="9696450" y="37985700"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1119,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="34582100"/>
+    <pos x="11544300" y="37985700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1139,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="34582100"/>
+    <pos x="13392150" y="37985700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1159,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="36429950"/>
+    <pos x="7848600" y="39833550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1179,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="36429950"/>
+    <pos x="9696450" y="39833550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1199,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="40767000"/>
+    <pos x="7848600" y="44551600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1219,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="40767000"/>
+    <pos x="9696450" y="44551600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1239,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="40767000"/>
+    <pos x="11544300" y="44551600"/>
     <ext cx="1809750" cy="1057275"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1259,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="40767000"/>
+    <pos x="13392150" y="44551600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1279,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="42614850"/>
+    <pos x="7848600" y="46399450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1299,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="42614850"/>
+    <pos x="9696450" y="46399450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1319,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="42614850"/>
+    <pos x="11544300" y="46399450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="42614850"/>
+    <pos x="13392150" y="46399450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="44462700"/>
+    <pos x="7848600" y="48247300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="44462700"/>
+    <pos x="9696450" y="48247300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="44462700"/>
+    <pos x="11544300" y="48247300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="61379100"/>
+    <pos x="7848600" y="65951100"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="65735200"/>
+    <pos x="7848600" y="70510400"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="65735200"/>
+    <pos x="9696450" y="70510400"/>
     <ext cx="1809750" cy="1133475"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="65735200"/>
+    <pos x="11544300" y="70510400"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="72123300"/>
+    <pos x="7848600" y="77482700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="72123300"/>
+    <pos x="9696450" y="77482700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="72123300"/>
+    <pos x="11544300" y="77482700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="72123300"/>
+    <pos x="13392150" y="77482700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="73971150"/>
+    <pos x="7848600" y="79330550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="73971150"/>
+    <pos x="9696450" y="79330550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="73971150"/>
+    <pos x="11544300" y="79330550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="73971150"/>
+    <pos x="13392150" y="79330550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="75819000"/>
+    <pos x="7848600" y="81178400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="75819000"/>
+    <pos x="9696450" y="81178400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="75819000"/>
+    <pos x="11544300" y="81178400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="86639400"/>
+    <pos x="7848600" y="92176600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="86639400"/>
+    <pos x="9696450" y="92176600"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="86639400"/>
+    <pos x="11544300" y="92176600"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="86639400"/>
+    <pos x="13392150" y="92176600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="88487250"/>
+    <pos x="7848600" y="94024450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="88487250"/>
+    <pos x="9696450" y="94024450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="88487250"/>
+    <pos x="11544300" y="94024450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="88487250"/>
+    <pos x="13392150" y="94024450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="90335100"/>
+    <pos x="7848600" y="95872300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2071,100 +2190,185 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D129"/>
+  <dimension ref="A1:F143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>블랙헤드 매끈  파우더    ↗ 원본</t>
+          <t>━  기타(미분류) 골격 치트시트  (이 파일 11종 기준)  ━</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>재료</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>용량</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>대체재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>베이킹 파우더 / (소다)</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>300g</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>강,바다에 있는 소금(미네럴)일종. / 연마, 중화, 탈취 등등의 효과. / 약알카리</t>
-        </is>
-      </c>
+          <t>전형 구성(%):  수상 17~67% · 유화 1~2% · 보습 6~6% · 활성 19~75% · 향 2~2% · 점증/pH 1~1% · 기타 2~99%</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>자주 쓰는 원료:  아로마베이스70×4 · 멘톨×3 · 라벤더에센셜오일×3 · 아로마베이스95×3 · 식물성글리세린×3 · 티트리에센셜오일×2 · 로즈워터×2 · 하이셀×2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>레몬 EO 또는 / 오렌지EO</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>3ml</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>60방울, 레몬껍질 오일</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>원하는 / 에센셜오일.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="14" customHeight="1">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>블랙헤드 매끈  파우더    ↗ 원본</t>
         </is>
       </c>
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="320" customHeight="1">
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>재료</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>용량</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>대체재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>베이킹 파우더 / (소다)</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>300g</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>강,바다에 있는 소금(미네럴)일종. / 연마, 중화, 탈취 등등의 효과. / 약알카리</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>레몬 EO 또는 / 오렌지EO</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>3ml</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>60방울, 레몬껍질 오일</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>원하는 / 에센셜오일.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="14" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  향 1 · 기타 99</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+    </row>
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+    </row>
+    <row r="11" ht="320" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>베이킹 소다는
 호수나 바다에 물이 증발하고 남은 천연 침전물인
@@ -2189,18 +2393,20 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>1. 지퍼백이나 비닐봉지에 베이킹 소다를 계량하세요.
 2. 에센셜오일과 입욕제 등을 넣어주세요.
@@ -2208,149 +2414,225 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="6" customHeight="1"/>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>자운유 모물엔    ↗ 원본</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t>살균, 소독, / 멘톨 녹이는 용도</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="F17" s="17" t="n"/>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>멘톨</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>0.5g</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>민트류의 화한 휘발성 성분. / 36개월 이하 어린이와 임산부는 빼고 만들어주세요.</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="F18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>자운고 인퓨즈오일</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t>피부트러블에 좋은 8종 약재 호호바, 해바라기오일 등에 담궈 유효성분 우려냄.</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="F19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>15방울</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>진정, 가려움완화</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>15방울</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="22" ht="14" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  활성 38 · 향 19 · 기타 44</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
+    </row>
+    <row r="23" ht="14" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="176" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="176" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>--&gt;
 기존 카렌듈라오일을 주재료로
@@ -2365,22 +2647,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="21" t="n"/>
+      <c r="F24" s="21" t="n"/>
+    </row>
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="128" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+    </row>
+    <row r="26" ht="128" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>1. 종이에 멘톨을 계량하세요.
 2. 아로마베이스70을 계량하고
@@ -2392,219 +2678,327 @@
 8. 벌레 물린 곳에 발라주세요.</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+    </row>
+    <row r="27" ht="6" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>로즈여성세정제    [워터류]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="48" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="30" ht="64" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>순수한 물 , / 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>장미수</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>내추럴 셀룰로오즈</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n"/>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="F32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>멘톨</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>0.1g</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>민트의 알콜성분.</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>유화제 멘톨이 워터와 섞이게</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>약쑥추출물</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>민감,진정</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>감초추출물</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>민감,진정</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>헥산디올</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>보습, 균번식억제</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="14" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 81 · 유화 1 · 활성 15 · 점증/pH 1 · 기타 2</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n"/>
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="13" t="n"/>
+    </row>
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="176" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+    </row>
+    <row r="40" ht="160" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>로즈워터, 쑥, 감초 등 천연한방성분이
 함유 되어있고 젤타입니다.
@@ -2615,18 +3009,20 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-    </row>
-    <row r="35" ht="208" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+    </row>
+    <row r="42" ht="208" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>만들기과정
 1.워터, 하이셀을 계량합니다.
@@ -2643,139 +3039,205 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="6" customHeight="1"/>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>로맨틱 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>곡물발효.</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="F46" s="17" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출. 장미의 수용성성분다량</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="F47" s="17" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑워터</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D48" s="25" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>로즈제라늄</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>30방울</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>피지균형, 호르몬균형</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="F49" s="17" t="inlineStr">
         <is>
           <t>일랑일랑에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 기타 2</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n"/>
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="13" t="n"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-    </row>
-    <row r="44" ht="240" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="15" t="n"/>
+    </row>
+    <row r="52" ht="224" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -2793,22 +3255,26 @@
 '방향제'로도요^^</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-    </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="21" t="n"/>
+      <c r="F52" s="21" t="n"/>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-    </row>
-    <row r="46" ht="80" customHeight="1">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="15" t="n"/>
+    </row>
+    <row r="54" ht="80" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95와
@@ -2817,165 +3283,243 @@
 4. 흔들어주면 완성.</t>
         </is>
       </c>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-    </row>
-    <row r="47" ht="6" customHeight="1"/>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="21" t="n"/>
+      <c r="F54" s="21" t="n"/>
+    </row>
+    <row r="55" ht="6" customHeight="1"/>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>리프레쉬 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n"/>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="D58" s="19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>곡물발효</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>편백워터</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>피톤치드 함유, 편백잎을 수증기추출</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>로즈마리워터</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D60" s="25" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>라임에센셜오일</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>라임껍질오일, 기분전환</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>버가못, 레몬EO</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>스피아민트에센셜오일</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="14" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="63" ht="14" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 향 2</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="13" t="n"/>
+      <c r="D63" s="13" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="13" t="n"/>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B55" s="6" t="n"/>
-      <c r="C55" s="6" t="n"/>
-      <c r="D55" s="6" t="n"/>
-    </row>
-    <row r="56" ht="176" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
+      <c r="B64" s="15" t="n"/>
+      <c r="C64" s="15" t="n"/>
+      <c r="D64" s="15" t="n"/>
+      <c r="E64" s="15" t="n"/>
+      <c r="F64" s="15" t="n"/>
+    </row>
+    <row r="65" ht="176" customHeight="1">
+      <c r="A65" s="16" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -2991,18 +3535,20 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-    </row>
-    <row r="58" ht="80" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="15" t="n"/>
+      <c r="D66" s="15" t="n"/>
+      <c r="E66" s="15" t="n"/>
+      <c r="F66" s="15" t="n"/>
+    </row>
+    <row r="67" ht="80" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95와
@@ -3012,161 +3558,237 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="6" customHeight="1"/>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="1" t="inlineStr">
+    <row r="68" ht="6" customHeight="1"/>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>릴렉스 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n"/>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n"/>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr">
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
         <is>
           <t>곡물발효</t>
         </is>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="F71" s="17" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
         <is>
           <t>진정, 라벤더꽃을 수증기증류추출</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="F72" s="17" t="inlineStr">
         <is>
           <t>어성초우린물, 캐모마일워터 등</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="73" ht="48" customHeight="1">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B73" s="17" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D73" s="25" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>오렌지에센셜오일</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
         <is>
           <t>오렌지껍질압착, 달콤한 향</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="F74" s="17" t="inlineStr">
         <is>
           <t>버가못, 레몬EO</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
         <is>
           <t>라벤더꽃에서 추출,진정, 불면증 도움</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="F75" s="17" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 향 2</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="n"/>
+      <c r="C76" s="13" t="n"/>
+      <c r="D76" s="13" t="n"/>
+      <c r="E76" s="13" t="n"/>
+      <c r="F76" s="13" t="n"/>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-    </row>
-    <row r="68" ht="208" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="B77" s="15" t="n"/>
+      <c r="C77" s="15" t="n"/>
+      <c r="D77" s="15" t="n"/>
+      <c r="E77" s="15" t="n"/>
+      <c r="F77" s="15" t="n"/>
+    </row>
+    <row r="78" ht="208" customHeight="1">
+      <c r="A78" s="20" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -3183,22 +3805,26 @@
 '방향제'로도요^^</t>
         </is>
       </c>
-      <c r="B68" s="10" t="n"/>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="10" t="n"/>
-    </row>
-    <row r="69" ht="14" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="B78" s="21" t="n"/>
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="21" t="n"/>
+      <c r="E78" s="21" t="n"/>
+      <c r="F78" s="21" t="n"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-    </row>
-    <row r="70" ht="80" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="B79" s="15" t="n"/>
+      <c r="C79" s="15" t="n"/>
+      <c r="D79" s="15" t="n"/>
+      <c r="E79" s="15" t="n"/>
+      <c r="F79" s="15" t="n"/>
+    </row>
+    <row r="80" ht="80" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95
@@ -3207,91 +3833,139 @@
 4. 흔들어주면 완성.</t>
         </is>
       </c>
-      <c r="B70" s="10" t="n"/>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="10" t="n"/>
-    </row>
-    <row r="71" ht="6" customHeight="1"/>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="1" t="inlineStr">
+      <c r="B80" s="21" t="n"/>
+      <c r="C80" s="21" t="n"/>
+      <c r="D80" s="21" t="n"/>
+      <c r="E80" s="21" t="n"/>
+      <c r="F80" s="21" t="n"/>
+    </row>
+    <row r="81" ht="6" customHeight="1"/>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>계피 진드기ZERO 스프레이    [100ml / 용기기준]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B72" s="2" t="n"/>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+      <c r="E82" s="6" t="n"/>
+      <c r="F82" s="6" t="n"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="272" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="84" ht="304" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>계피에센셜오일 / (시나몬오일)</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>40방울 / (2ml)</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>녹나무과 식물이고 나무껍질을 주로 활용. / 중국,스리랑카, 인도, 동남아시아가 원산지죠. / 계피 나무껍질 향은 상당히 강하고 달콤하면서 맵습니다. / 계피의 나무껍질을 수증기증류법으로 추출하면몇십배 농축된 계피오일을 추출할 수 있습니다.주성분이 시남알데히드(cinnamaldehyde)로 80~90%을 차지. 알데하이드성분은 벌레퇴치,항진균효과가 탁월. 계피오일은 예로부터 강력한 살균, 항진균, 방충, 소화촉진 마취, 방부효과가 있어 활용한 예가 많습니다. / 단, 고농축인 계피오일은 피부자극이 있기 때문에 피부에 직접 사용하는 것은 피해주세요. / 임산부도 사용을 금합니다.</t>
         </is>
       </c>
-      <c r="D74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="F84" s="8" t="n"/>
+    </row>
+    <row r="85" ht="48" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="D85" s="26" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>보존제, 희석용매, 오일이 분리되지 않고 잘 분산이 되도록 함.</t>
         </is>
       </c>
-      <c r="D75" s="4" t="n"/>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="F85" s="8" t="n"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  향 2 · 방부 98</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="n"/>
+      <c r="C86" s="13" t="n"/>
+      <c r="D86" s="13" t="n"/>
+      <c r="E86" s="13" t="n"/>
+      <c r="F86" s="13" t="n"/>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-    </row>
-    <row r="77" ht="384" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="B87" s="15" t="n"/>
+      <c r="C87" s="15" t="n"/>
+      <c r="D87" s="15" t="n"/>
+      <c r="E87" s="15" t="n"/>
+      <c r="F87" s="15" t="n"/>
+    </row>
+    <row r="88" ht="384" customHeight="1">
+      <c r="A88" s="16" t="inlineStr">
         <is>
           <t>큰아이 다은이는 코막힘, 콧물 증상 때문에 병원에 한번씩 가면
 담당 의사선생님이 감기약보다 알르레기 비염약도 항상 처방을 해주셨어요.
@@ -3320,8 +3994,8 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="384" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+    <row r="89" ht="384" customHeight="1">
+      <c r="A89" s="16" t="inlineStr">
         <is>
           <t>어미진드기는 3주마다 새진드기를 낳습니다. 어마어한 놈입니다.ㅠㅠ
 여러 매체에서 소개된 각종 알레르기 질환의 주범인
@@ -3350,8 +4024,8 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="336" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="90" ht="336" customHeight="1">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>중국, 스리랑카, 인도, 동남아시아가 원산지죠.
 계피 나무껍질,잎의 향은 상당히 강하고 달콤하면서 맵습니다.
@@ -3377,18 +4051,20 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="14" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="6" t="n"/>
-    </row>
-    <row r="81" ht="144" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="15" t="n"/>
+      <c r="D91" s="15" t="n"/>
+      <c r="E91" s="15" t="n"/>
+      <c r="F91" s="15" t="n"/>
+    </row>
+    <row r="92" ht="144" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
         <is>
           <t>계피스프레이 초정밀 만들기과정
 [100ml 용기기준]
@@ -3402,95 +4078,121 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="6" customHeight="1"/>
-    <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="1" t="inlineStr">
+    <row r="93" ht="6" customHeight="1"/>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>어성초팅크처    ↗ 원본</t>
         </is>
       </c>
-      <c r="B83" s="2" t="n"/>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n"/>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="F94" s="6" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+    <row r="96" ht="64" customHeight="1">
+      <c r="A96" s="17" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B96" s="17" t="inlineStr">
         <is>
           <t>7.41%</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C96" s="18" t="inlineStr"/>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
         <is>
           <t>어성초 추출, 물고기 비린내가 난다하여 어성초, 각종 피부트러블, 피부 개선에 사용</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="F96" s="17" t="inlineStr">
         <is>
           <t>녹차, 병풀, 알란토인,카렌듈라추출물, 유기농 프레쉬 5솔루션 등</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="17" t="inlineStr">
         <is>
           <t>에탄올(변성)</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B97" s="17" t="inlineStr">
         <is>
           <t>92.59%</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C97" s="18" t="inlineStr"/>
+      <c r="D97" s="27" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="E97" s="17" t="inlineStr">
         <is>
           <t>가용화제, / 물에 오일이 골고루 분산</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="F97" s="17" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-    </row>
-    <row r="88" ht="144" customHeight="1">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="B98" s="15" t="n"/>
+      <c r="C98" s="15" t="n"/>
+      <c r="D98" s="15" t="n"/>
+      <c r="E98" s="15" t="n"/>
+      <c r="F98" s="15" t="n"/>
+    </row>
+    <row r="99" ht="144" customHeight="1">
+      <c r="A99" s="20" t="inlineStr">
         <is>
           <t>◎ 이렇게 잘 만들어진 어성초팅크처
 1. 보관기간은 알콜이기 때문에 1년이상 보관하실 수 있구요.
@@ -3499,285 +4201,417 @@
 4. 더 진하게 만들고 싶다면.. 담그고 2주 후 어성초건초를 빼내고 새로운 어성초 40g정도를 넣어주세요. 또 2주나 한달을 숙성하시면 되요. 그러면 한번한 것보다는 팅크처를 진하게 만들 수 있어요. ^^</t>
         </is>
       </c>
-      <c r="B88" s="10" t="n"/>
-      <c r="C88" s="10" t="n"/>
-      <c r="D88" s="10" t="n"/>
-    </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="B99" s="21" t="n"/>
+      <c r="C99" s="21" t="n"/>
+      <c r="D99" s="21" t="n"/>
+      <c r="E99" s="21" t="n"/>
+      <c r="F99" s="21" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-    </row>
-    <row r="90" ht="48" customHeight="1">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="B100" s="15" t="n"/>
+      <c r="C100" s="15" t="n"/>
+      <c r="D100" s="15" t="n"/>
+      <c r="E100" s="15" t="n"/>
+      <c r="F100" s="15" t="n"/>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="20" t="inlineStr">
         <is>
           <t>1. 어성초건초 40g을 병에 눌러 담는다.
 2. 병에 식물성에탄올(순수발효주정) 500g 넣는다.
 3. 2주나 한달정도 숙성하면 완성!(그늘지고 서늘한 곳에서 보관요)</t>
         </is>
       </c>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="10" t="n"/>
-    </row>
-    <row r="91" ht="6" customHeight="1"/>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="B101" s="21" t="n"/>
+      <c r="C101" s="21" t="n"/>
+      <c r="D101" s="21" t="n"/>
+      <c r="E101" s="21" t="n"/>
+      <c r="F101" s="21" t="n"/>
+    </row>
+    <row r="102" ht="6" customHeight="1"/>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
         <is>
           <t>아로마 물파스    ↗ 원본</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="B103" s="6" t="n"/>
+      <c r="C103" s="6" t="n"/>
+      <c r="D103" s="6" t="n"/>
+      <c r="E103" s="6" t="n"/>
+      <c r="F103" s="6" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>위치헤이즐워터</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="F105" s="8" t="inlineStr">
         <is>
           <t>편백워터</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>알로에겔(국내거제산)</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>수분공급,진정</t>
         </is>
       </c>
-      <c r="D95" s="4" t="n"/>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="F106" s="8" t="n"/>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D107" s="23" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>점증제</t>
         </is>
       </c>
-      <c r="D96" s="4" t="n"/>
-    </row>
-    <row r="97" ht="64" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="F107" s="8" t="n"/>
+    </row>
+    <row r="108" ht="64" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>멘톨</t>
         </is>
       </c>
-      <c r="B97" s="4" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>박하뇌라고도하고 알콜성분, 박하의 잎, 꽃에서 수증기 증류하여 얻어진다. 물에 녹지않고 진통제 가려움증을 멈추는데 사용</t>
         </is>
       </c>
-      <c r="D97" s="4" t="n"/>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+      <c r="F108" s="8" t="n"/>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>식물성에탄올</t>
         </is>
       </c>
-      <c r="B98" s="4" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>16g</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E109" s="8" t="inlineStr">
         <is>
           <t>곡물발효주정, 소주원액, 소독</t>
         </is>
       </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="F109" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>인플라신</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
         <is>
           <t>항염</t>
         </is>
       </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="F110" s="8" t="inlineStr">
         <is>
           <t>알란토인</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="4" t="inlineStr">
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B100" s="4" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D111" s="24" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
         <is>
           <t>가용화제, 워터와 오일들 분리저지</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="F111" s="8" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="F112" s="8" t="inlineStr">
         <is>
           <t>캐모마일로먼,저먼</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B102" s="4" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C113" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="F113" s="8" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="114" ht="32" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>로즈마리에센셜오일</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C114" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
         <is>
           <t>혈액순환</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="F114" s="8" t="inlineStr">
         <is>
           <t>페파민트 등</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="14" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 67 · 유화 2 · 활성 19 · 향 2 · 점증/pH 1 · 기타 10</t>
+        </is>
+      </c>
+      <c r="B115" s="13" t="n"/>
+      <c r="C115" s="13" t="n"/>
+      <c r="D115" s="13" t="n"/>
+      <c r="E115" s="13" t="n"/>
+      <c r="F115" s="13" t="n"/>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B104" s="6" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="6" t="n"/>
-    </row>
-    <row r="105" ht="80" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="B116" s="15" t="n"/>
+      <c r="C116" s="15" t="n"/>
+      <c r="D116" s="15" t="n"/>
+      <c r="E116" s="15" t="n"/>
+      <c r="F116" s="15" t="n"/>
+    </row>
+    <row r="117" ht="80" customHeight="1">
+      <c r="A117" s="16" t="inlineStr">
         <is>
           <t>[ 레시피 재료 ]
 ① 위치헤이즐워터 50g, 천연알로에베라원액 20g, 하이셀 1g
@@ -3786,18 +4620,20 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="14" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B106" s="6" t="n"/>
-      <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="n"/>
-    </row>
-    <row r="107" ht="128" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
+      <c r="B118" s="15" t="n"/>
+      <c r="C118" s="15" t="n"/>
+      <c r="D118" s="15" t="n"/>
+      <c r="E118" s="15" t="n"/>
+      <c r="F118" s="15" t="n"/>
+    </row>
+    <row r="119" ht="128" customHeight="1">
+      <c r="A119" s="16" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 알로에겔, 위치헤이즐워터, 하이셀을 계량한다.
@@ -3810,91 +4646,137 @@
         </is>
       </c>
     </row>
-    <row r="108" ht="6" customHeight="1"/>
-    <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="1" t="inlineStr">
+    <row r="120" ht="6" customHeight="1"/>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>데일리 스마트폰 소독제    [100ml기준]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n"/>
-      <c r="C109" s="2" t="n"/>
-      <c r="D109" s="2" t="n"/>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="B121" s="6" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+      <c r="E121" s="6" t="n"/>
+      <c r="F121" s="6" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="8" t="inlineStr">
+    <row r="123" ht="32" customHeight="1">
+      <c r="A123" s="17" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B123" s="17" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C111" s="8" t="inlineStr">
+      <c r="C123" s="18" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E123" s="17" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼향, 기분전환, / 항균^^</t>
         </is>
       </c>
-      <c r="D111" s="8" t="inlineStr">
+      <c r="F123" s="17" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="32" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="17" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B124" s="17" t="inlineStr">
         <is>
           <t>100ml(87g)</t>
         </is>
       </c>
-      <c r="C112" s="8" t="inlineStr">
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="D124" s="10" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
         <is>
           <t>소독,살균</t>
         </is>
       </c>
-      <c r="D112" s="8" t="n"/>
-    </row>
-    <row r="113" ht="14" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="F124" s="17" t="n"/>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  향 1 · 기타 99</t>
+        </is>
+      </c>
+      <c r="B125" s="13" t="n"/>
+      <c r="C125" s="13" t="n"/>
+      <c r="D125" s="13" t="n"/>
+      <c r="E125" s="13" t="n"/>
+      <c r="F125" s="13" t="n"/>
+    </row>
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6" t="n"/>
-    </row>
-    <row r="114" ht="384" customHeight="1">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="B126" s="15" t="n"/>
+      <c r="C126" s="15" t="n"/>
+      <c r="D126" s="15" t="n"/>
+      <c r="E126" s="15" t="n"/>
+      <c r="F126" s="15" t="n"/>
+    </row>
+    <row r="127" ht="384" customHeight="1">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>매일 사용하는 스마트폰이 화장실변기보다 세균과 바이러스가 10배이상 많이 검출된다는
 뉴스를 접한 적이 있어요. (뜨아~~)
@@ -3922,12 +4804,14 @@
 이 막은 에탄올이 세균 내부로 침투하는 것을 막습니다.</t>
         </is>
       </c>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="10" t="n"/>
-      <c r="D114" s="10" t="n"/>
-    </row>
-    <row r="115" ht="384" customHeight="1">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="B127" s="21" t="n"/>
+      <c r="C127" s="21" t="n"/>
+      <c r="D127" s="21" t="n"/>
+      <c r="E127" s="21" t="n"/>
+      <c r="F127" s="21" t="n"/>
+    </row>
+    <row r="128" ht="384" customHeight="1">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>따라서 살균작용이 효과적으로 일어나게 하려면 순수 에탄올에 물을 섞어야 한답니다.
 세균 표면의 막을 한꺼번에 응고시키는 것을 막아고
@@ -3955,33 +4839,39 @@
 방법은 같습니다.</t>
         </is>
       </c>
-      <c r="B115" s="10" t="n"/>
-      <c r="C115" s="10" t="n"/>
-      <c r="D115" s="10" t="n"/>
-    </row>
-    <row r="116" ht="32" customHeight="1">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="B128" s="21" t="n"/>
+      <c r="C128" s="21" t="n"/>
+      <c r="D128" s="21" t="n"/>
+      <c r="E128" s="21" t="n"/>
+      <c r="F128" s="21" t="n"/>
+    </row>
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="20" t="inlineStr">
         <is>
           <t>면거즈나 (키친타올이나) 티슈에 촉촉할 정도로 적셔서
 닦아주세요.</t>
         </is>
       </c>
-      <c r="B116" s="10" t="n"/>
-      <c r="C116" s="10" t="n"/>
-      <c r="D116" s="10" t="n"/>
-    </row>
-    <row r="117" ht="14" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="B129" s="21" t="n"/>
+      <c r="C129" s="21" t="n"/>
+      <c r="D129" s="21" t="n"/>
+      <c r="E129" s="21" t="n"/>
+      <c r="F129" s="21" t="n"/>
+    </row>
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B117" s="6" t="n"/>
-      <c r="C117" s="6" t="n"/>
-      <c r="D117" s="6" t="n"/>
-    </row>
-    <row r="118" ht="208" customHeight="1">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="B130" s="15" t="n"/>
+      <c r="C130" s="15" t="n"/>
+      <c r="D130" s="15" t="n"/>
+      <c r="E130" s="15" t="n"/>
+      <c r="F130" s="15" t="n"/>
+    </row>
+    <row r="131" ht="208" customHeight="1">
+      <c r="A131" s="20" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.용기에 에센셜오일을 20방울 떨어뜨려주세요. (에센셜오일을 넣지 않는다면 생략 가능)
@@ -3997,117 +4887,175 @@
 오랜만에 닦으니 어찌나 지저분한지.. 상큼한 레몬 잔향이 기분좋게 만드네요.</t>
         </is>
       </c>
-      <c r="B118" s="10" t="n"/>
-      <c r="C118" s="10" t="n"/>
-      <c r="D118" s="10" t="n"/>
-    </row>
-    <row r="119" ht="6" customHeight="1"/>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="1" t="inlineStr">
+      <c r="B131" s="21" t="n"/>
+      <c r="C131" s="21" t="n"/>
+      <c r="D131" s="21" t="n"/>
+      <c r="E131" s="21" t="n"/>
+      <c r="F131" s="21" t="n"/>
+    </row>
+    <row r="132" ht="6" customHeight="1"/>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>아로마 손소독제스프레이    ↗ 원본</t>
         </is>
       </c>
-      <c r="B120" s="2" t="n"/>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n"/>
-    </row>
-    <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="B133" s="6" t="n"/>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="6" t="n"/>
+      <c r="E133" s="6" t="n"/>
+      <c r="F133" s="6" t="n"/>
+    </row>
+    <row r="134" ht="15" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="F134" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="64" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
+    <row r="135" ht="64" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>465ml</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
         <is>
           <t>곡물 발효 , / 소독효과가 제일 좋은 70% 알코올함량, / 에센셜오일 분산, 방향용으로 사용시 / 공기정화, 소독효과.</t>
         </is>
       </c>
-      <c r="D122" s="4" t="n"/>
-    </row>
-    <row r="123" ht="48" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="48" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>22.5g</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D136" s="25" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
         <is>
           <t>손 보습제, 향과 알코올이 오랫동안 머물 수 / 있도록 고착제 역할을 함.</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="F136" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
+    <row r="137" ht="48" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>(레몬) 에센셜오일</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>2~5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 / 천연오일. 원하는 향.</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="F137" s="8" t="inlineStr">
         <is>
           <t>클린코튼, 그린티시트러스, 체리블라썸 향 등</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  보습 5 · 향 95</t>
+        </is>
+      </c>
+      <c r="B138" s="13" t="n"/>
+      <c r="C138" s="13" t="n"/>
+      <c r="D138" s="13" t="n"/>
+      <c r="E138" s="13" t="n"/>
+      <c r="F138" s="13" t="n"/>
+    </row>
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="14" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6" t="n"/>
-    </row>
-    <row r="126" ht="384" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
+      <c r="B139" s="15" t="n"/>
+      <c r="C139" s="15" t="n"/>
+      <c r="D139" s="15" t="n"/>
+      <c r="E139" s="15" t="n"/>
+      <c r="F139" s="15" t="n"/>
+    </row>
+    <row r="140" ht="384" customHeight="1">
+      <c r="A140" s="16" t="inlineStr">
         <is>
           <t>2009년 신종 플루 때 안내해드린 레시피입니다.
 이번 메르스, 신종 플루 때처럼 사람들을 불안하게 하네요.
@@ -4131,15 +5079,15 @@
 따라서 살균작용이 효과적으로 일어나게 하려면 순수 에탄올에 물을 섞어야 합니다.
 세균 표면의 막을 한꺼번에 응고시키는 것을 막고
 에탄올 분자가 세균의 체내로 뚫고 들어갈 수 있게 하는 것입니다.
-에탄올은 70%정도가 가장 강한 살균력을 나타내며,</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="112" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>60% 이하나, 80% 이상에서는 거의 살균력이 없습니다.
-에탄올 80%이상에서 살균분무시 알콜성분이 빨리 공기 중에
+에탄올은 70%정도가 가장 강한 살균력을 나타내며,
+60% 이하나, 80% 이상에서는 거의 살균력이 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="96" customHeight="1">
+      <c r="A141" s="16" t="inlineStr">
+        <is>
+          <t>에탄올 80%이상에서 살균분무시 알콜성분이 빨리 공기 중에
 증발하여 지속적인 살균이 어렵기도 하답니다.
 이점 참고하세요.
 허브누리 회원님들
@@ -4148,18 +5096,20 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="14" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B128" s="6" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-    </row>
-    <row r="129" ht="160" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="B142" s="15" t="n"/>
+      <c r="C142" s="15" t="n"/>
+      <c r="D142" s="15" t="n"/>
+      <c r="E142" s="15" t="n"/>
+      <c r="F142" s="15" t="n"/>
+    </row>
+    <row r="143" ht="160" customHeight="1">
+      <c r="A143" s="16" t="inlineStr">
         <is>
           <t>초간단 만들기과정
 1. 아로마베이스70 속/겉뚜껑을 열고
@@ -4173,82 +5123,95 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="6" customHeight="1"/>
+    <row r="144" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A106:D106"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A109:D109"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A83:D83"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A107:D107"/>
-    <mergeCell ref="A60:D60"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A128:D128"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A90:D90"/>
-    <mergeCell ref="A80:D80"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A118:D118"/>
-    <mergeCell ref="A120:D120"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A32:D32"/>
+  <mergeCells count="73">
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A130:F130"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>

--- a/카드_아키타입/00_기타(미분류).xlsx
+++ b/카드_아키타입/00_기타(미분류).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,10 @@
     </font>
     <font>
       <color rgb="003A3A3A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="007A4A2A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -55,7 +59,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECE0"/>
       </patternFill>
     </fill>
     <fill>
@@ -169,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -179,11 +188,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -192,39 +205,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -238,6 +248,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -319,7 +332,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7848600" y="1092200"/>
+    <pos x="7848600" y="1663700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -339,7 +352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="1092200"/>
+    <pos x="9696450" y="1663700"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -359,7 +372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="1092200"/>
+    <pos x="11544300" y="1663700"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -379,7 +392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="1092200"/>
+    <pos x="13392150" y="1663700"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -399,7 +412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="2940050"/>
+    <pos x="7848600" y="3511549"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -419,7 +432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="7861300"/>
+    <pos x="7848600" y="8432800"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -439,7 +452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="7861300"/>
+    <pos x="9696450" y="8432800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -459,7 +472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="7861300"/>
+    <pos x="11544300" y="8432800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -479,7 +492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="7861300"/>
+    <pos x="13392150" y="8432800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -499,7 +512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="9709150"/>
+    <pos x="7848600" y="10280650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -519,7 +532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="9709150"/>
+    <pos x="9696450" y="10280650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -539,7 +552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="9709150"/>
+    <pos x="11544300" y="10280650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -559,7 +572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="9709150"/>
+    <pos x="13392150" y="10280650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -579,7 +592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="11557000"/>
+    <pos x="7848600" y="12128500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -599,7 +612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="11557000"/>
+    <pos x="9696450" y="12128500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -619,7 +632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="11557000"/>
+    <pos x="11544300" y="12128500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -639,7 +652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="15443200"/>
+    <pos x="7848600" y="16014700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -659,7 +672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="15443200"/>
+    <pos x="9696450" y="16014700"/>
     <ext cx="1809750" cy="1266825"/>
     <pic>
       <nvPicPr>
@@ -679,7 +692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="15443200"/>
+    <pos x="11544300" y="16014700"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -699,7 +712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="15443200"/>
+    <pos x="13392150" y="16014700"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -719,7 +732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="17291050"/>
+    <pos x="7848600" y="17862550"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -739,7 +752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="17291050"/>
+    <pos x="9696450" y="17862550"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -759,7 +772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="17291050"/>
+    <pos x="11544300" y="17862550"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -779,7 +792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="17291050"/>
+    <pos x="13392150" y="17862550"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -799,7 +812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="19138900"/>
+    <pos x="7848600" y="19710399"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -819,7 +832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="19138900"/>
+    <pos x="9696450" y="19710399"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -839,7 +852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="25260300"/>
+    <pos x="7848600" y="25831800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -859,7 +872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="25260300"/>
+    <pos x="9696450" y="25831800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -879,7 +892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="25260300"/>
+    <pos x="11544300" y="25831800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -899,7 +912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="25260300"/>
+    <pos x="13392150" y="25831800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -919,7 +932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="27108150"/>
+    <pos x="7848600" y="27679650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -939,7 +952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="27108150"/>
+    <pos x="9696450" y="27679650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -959,7 +972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="31826200"/>
+    <pos x="7848600" y="32397700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -979,7 +992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="31826200"/>
+    <pos x="9696450" y="32397700"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -999,7 +1012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="31826200"/>
+    <pos x="11544300" y="32397700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1019,7 +1032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="31826200"/>
+    <pos x="13392150" y="32397700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1039,7 +1052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="33674050"/>
+    <pos x="7848600" y="34245550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1059,7 +1072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="33674050"/>
+    <pos x="9696450" y="34245550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1079,7 +1092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="37985700"/>
+    <pos x="7848600" y="38557200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1099,7 +1112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="37985700"/>
+    <pos x="9696450" y="38557200"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1119,7 +1132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="37985700"/>
+    <pos x="11544300" y="38557200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1139,7 +1152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="37985700"/>
+    <pos x="13392150" y="38557200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1159,7 +1172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="39833550"/>
+    <pos x="7848600" y="40405050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1179,7 +1192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="39833550"/>
+    <pos x="9696450" y="40405050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1199,7 +1212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="44551600"/>
+    <pos x="7848600" y="45123100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1219,7 +1232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="44551600"/>
+    <pos x="9696450" y="45123100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1239,7 +1252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="44551600"/>
+    <pos x="11544300" y="45123100"/>
     <ext cx="1809750" cy="1057275"/>
     <pic>
       <nvPicPr>
@@ -1259,7 +1272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="44551600"/>
+    <pos x="13392150" y="45123100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1279,7 +1292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="46399450"/>
+    <pos x="7848600" y="46970950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1299,7 +1312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="46399450"/>
+    <pos x="9696450" y="46970950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1319,7 +1332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="46399450"/>
+    <pos x="11544300" y="46970950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1339,7 +1352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="46399450"/>
+    <pos x="13392150" y="46970950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1359,7 +1372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="48247300"/>
+    <pos x="7848600" y="48818800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1379,7 +1392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="48247300"/>
+    <pos x="9696450" y="48818800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1399,7 +1412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="48247300"/>
+    <pos x="11544300" y="48818800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1419,7 +1432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="65951100"/>
+    <pos x="7848600" y="66522600"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1439,7 +1452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="70510400"/>
+    <pos x="7848600" y="71081900"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1459,7 +1472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="70510400"/>
+    <pos x="9696450" y="71081900"/>
     <ext cx="1809750" cy="1133475"/>
     <pic>
       <nvPicPr>
@@ -1479,7 +1492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="70510400"/>
+    <pos x="11544300" y="71081900"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1499,7 +1512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="77482700"/>
+    <pos x="7848600" y="78054200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1519,7 +1532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="77482700"/>
+    <pos x="9696450" y="78054200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1539,7 +1552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="77482700"/>
+    <pos x="11544300" y="78054200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1559,7 +1572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="77482700"/>
+    <pos x="13392150" y="78054200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1579,7 +1592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="79330550"/>
+    <pos x="7848600" y="79902050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1599,7 +1612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="79330550"/>
+    <pos x="9696450" y="79902050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1619,7 +1632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="79330550"/>
+    <pos x="11544300" y="79902050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1639,7 +1652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="79330550"/>
+    <pos x="13392150" y="79902050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1659,7 +1672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="81178400"/>
+    <pos x="7848600" y="81749900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1679,7 +1692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="81178400"/>
+    <pos x="9696450" y="81749900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1699,7 +1712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="81178400"/>
+    <pos x="11544300" y="81749900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1719,7 +1732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="92176600"/>
+    <pos x="7848600" y="92748100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1739,7 +1752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="92176600"/>
+    <pos x="9696450" y="92748100"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1759,7 +1772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="92176600"/>
+    <pos x="11544300" y="92748100"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1779,7 +1792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="92176600"/>
+    <pos x="13392150" y="92748100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1799,7 +1812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="94024450"/>
+    <pos x="7848600" y="94595950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1819,7 +1832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="94024450"/>
+    <pos x="9696450" y="94595950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1839,7 +1852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="94024450"/>
+    <pos x="11544300" y="94595950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1859,7 +1872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="94024450"/>
+    <pos x="13392150" y="94595950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1879,7 +1892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="95872300"/>
+    <pos x="7848600" y="96443800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2190,7 +2203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2238,127 +2251,129 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
     </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 이 제형 배합 주의·기본원칙
+· 먼저 제형(수상/유상/무수/유화 여부)을 파악하고 해당 골격을 참고.
+· 기본 점검: 방부(물 있으면 필수)·pH·유화 온도.</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="6" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>블랙헤드 매끈  파우더    ↗ 원본</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>베이킹 파우더 / (소다)</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>300g</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>강,바다에 있는 소금(미네럴)일종. / 연마, 중화, 탈취 등등의 효과. / 약알카리</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>레몬 EO 또는 / 오렌지EO</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>3ml</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>60방울, 레몬껍질 오일</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>원하는 / 에센셜오일.</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  향 1 · 기타 99</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n"/>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13" t="n"/>
-      <c r="E9" s="13" t="n"/>
-      <c r="F9" s="13" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  향 1 · 기타 99</t>
         </is>
       </c>
       <c r="B10" s="15" t="n"/>
@@ -2367,8 +2382,20 @@
       <c r="E10" s="15" t="n"/>
       <c r="F10" s="15" t="n"/>
     </row>
-    <row r="11" ht="320" customHeight="1">
+    <row r="11" ht="14" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+    </row>
+    <row r="12" ht="320" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>베이킹 소다는
 호수나 바다에 물이 증발하고 남은 천연 침전물인
@@ -2393,20 +2420,20 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="15" t="n"/>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+    </row>
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>1. 지퍼백이나 비닐봉지에 베이킹 소다를 계량하세요.
 2. 에센셜오일과 입욕제 등을 넣어주세요.
@@ -2414,215 +2441,203 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="15" ht="6" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>자운유 모물엔    ↗ 원본</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>살균, 소독, / 멘톨 녹이는 용도</t>
         </is>
       </c>
-      <c r="F17" s="17" t="n"/>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="F18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>멘톨</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>0.5g</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>민트류의 화한 휘발성 성분. / 36개월 이하 어린이와 임산부는 빼고 만들어주세요.</t>
         </is>
       </c>
-      <c r="F18" s="17" t="n"/>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="F19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>자운고 인퓨즈오일</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>피부트러블에 좋은 8종 약재 호호바, 해바라기오일 등에 담궈 유효성분 우려냄.</t>
         </is>
       </c>
-      <c r="F19" s="17" t="n"/>
-    </row>
-    <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="F20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>15방울</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>진정, 가려움완화</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>15방울</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>9%</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  활성 38 · 향 19 · 기타 44</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
     </row>
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  활성 38 · 향 19 · 기타 44</t>
         </is>
       </c>
       <c r="B23" s="15" t="n"/>
@@ -2631,8 +2646,20 @@
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="15" t="n"/>
     </row>
-    <row r="24" ht="176" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+    </row>
+    <row r="25" ht="176" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>--&gt;
 기존 카렌듈라오일을 주재료로
@@ -2647,26 +2674,26 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B24" s="21" t="n"/>
-      <c r="C24" s="21" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="21" t="n"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n"/>
-      <c r="C25" s="15" t="n"/>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-    </row>
-    <row r="26" ht="128" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+    </row>
+    <row r="27" ht="128" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>1. 종이에 멘톨을 계량하세요.
 2. 아로마베이스70을 계량하고
@@ -2678,317 +2705,305 @@
 8. 벌레 물린 곳에 발라주세요.</t>
         </is>
       </c>
-      <c r="B26" s="21" t="n"/>
-      <c r="C26" s="21" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="21" t="n"/>
-    </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+    </row>
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>로즈여성세정제    [워터류]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
+      <c r="E29" s="8" t="n"/>
+      <c r="F29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="64" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="31" ht="64" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>순수한 물 , / 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D32" s="24" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>장미수</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>1.0g</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D32" s="23" t="inlineStr">
+      <c r="D33" s="25" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>내추럴 셀룰로오즈</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="F33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>멘톨</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>0.1g</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>민트의 알콜성분.</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="F34" s="10" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D34" s="24" t="inlineStr">
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>유화제 멘톨이 워터와 섞이게</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>약쑥추출물</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>8%</t>
         </is>
       </c>
-      <c r="D35" s="19" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>민감,진정</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="64" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>감초추출물</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>7g</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="D36" s="19" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>민감,진정</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="64" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>헥산디올</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>보습, 균번식억제</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 81 · 유화 1 · 활성 15 · 점증/pH 1 · 기타 2</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
     </row>
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 81 · 유화 1 · 활성 15 · 점증/pH 1 · 기타 2</t>
         </is>
       </c>
       <c r="B39" s="15" t="n"/>
@@ -2997,8 +3012,20 @@
       <c r="E39" s="15" t="n"/>
       <c r="F39" s="15" t="n"/>
     </row>
-    <row r="40" ht="160" customHeight="1">
+    <row r="40" ht="14" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+    </row>
+    <row r="41" ht="160" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>로즈워터, 쑥, 감초 등 천연한방성분이
 함유 되어있고 젤타입니다.
@@ -3009,20 +3036,20 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="14" customHeight="1">
-      <c r="A41" s="14" t="inlineStr">
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n"/>
-      <c r="C41" s="15" t="n"/>
-      <c r="D41" s="15" t="n"/>
-      <c r="E41" s="15" t="n"/>
-      <c r="F41" s="15" t="n"/>
-    </row>
-    <row r="42" ht="208" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+    </row>
+    <row r="43" ht="208" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>만들기과정
 1.워터, 하이셀을 계량합니다.
@@ -3039,195 +3066,183 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="6" customHeight="1"/>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="44" ht="6" customHeight="1"/>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>로맨틱 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="B45" s="8" t="n"/>
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="8" t="n"/>
+      <c r="F45" s="8" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D46" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C47" s="20" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
+      <c r="D47" s="21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>곡물발효.</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="D47" s="22" t="inlineStr">
+      <c r="D48" s="24" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E48" s="19" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출. 장미의 수용성성분다량</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑워터</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C49" s="20" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D48" s="25" t="inlineStr">
+      <c r="D49" s="27" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>로즈제라늄</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>30방울</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C50" s="20" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D49" s="10" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E50" s="19" t="inlineStr">
         <is>
           <t>피지균형, 호르몬균형</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>일랑일랑에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 기타 2</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="n"/>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
-      <c r="E50" s="13" t="n"/>
-      <c r="F50" s="13" t="n"/>
     </row>
     <row r="51" ht="14" customHeight="1">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 기타 2</t>
         </is>
       </c>
       <c r="B51" s="15" t="n"/>
@@ -3236,8 +3251,20 @@
       <c r="E51" s="15" t="n"/>
       <c r="F51" s="15" t="n"/>
     </row>
-    <row r="52" ht="224" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
+    </row>
+    <row r="53" ht="224" customHeight="1">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -3255,26 +3282,26 @@
 '방향제'로도요^^</t>
         </is>
       </c>
-      <c r="B52" s="21" t="n"/>
-      <c r="C52" s="21" t="n"/>
-      <c r="D52" s="21" t="n"/>
-      <c r="E52" s="21" t="n"/>
-      <c r="F52" s="21" t="n"/>
-    </row>
-    <row r="53" ht="14" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
+      <c r="B53" s="23" t="n"/>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="23" t="n"/>
+      <c r="E53" s="23" t="n"/>
+      <c r="F53" s="23" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B53" s="15" t="n"/>
-      <c r="C53" s="15" t="n"/>
-      <c r="D53" s="15" t="n"/>
-      <c r="E53" s="15" t="n"/>
-      <c r="F53" s="15" t="n"/>
-    </row>
-    <row r="54" ht="80" customHeight="1">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="17" t="n"/>
+    </row>
+    <row r="55" ht="80" customHeight="1">
+      <c r="A55" s="22" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95와
@@ -3283,233 +3310,221 @@
 4. 흔들어주면 완성.</t>
         </is>
       </c>
-      <c r="B54" s="21" t="n"/>
-      <c r="C54" s="21" t="n"/>
-      <c r="D54" s="21" t="n"/>
-      <c r="E54" s="21" t="n"/>
-      <c r="F54" s="21" t="n"/>
-    </row>
-    <row r="55" ht="6" customHeight="1"/>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="B55" s="23" t="n"/>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="23" t="n"/>
+      <c r="E55" s="23" t="n"/>
+      <c r="F55" s="23" t="n"/>
+    </row>
+    <row r="56" ht="6" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>리프레쉬 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="6" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D58" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E57" s="7" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B58" s="8" t="inlineStr">
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C59" s="11" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D58" s="19" t="inlineStr">
+      <c r="D59" s="21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E59" s="10" t="inlineStr">
         <is>
           <t>곡물발효</t>
         </is>
       </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="F59" s="10" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>편백워터</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="D59" s="22" t="inlineStr">
+      <c r="D60" s="24" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>피톤치드 함유, 편백잎을 수증기추출</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F60" s="10" t="inlineStr">
         <is>
           <t>로즈마리워터</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="48" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D60" s="25" t="inlineStr">
+      <c r="D61" s="27" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>라임에센셜오일</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>라임껍질오일, 기분전환</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>버가못, 레몬EO</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>스피아민트에센셜오일</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="14" customHeight="1">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 향 2</t>
-        </is>
-      </c>
-      <c r="B63" s="13" t="n"/>
-      <c r="C63" s="13" t="n"/>
-      <c r="D63" s="13" t="n"/>
-      <c r="E63" s="13" t="n"/>
-      <c r="F63" s="13" t="n"/>
     </row>
     <row r="64" ht="14" customHeight="1">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 향 2</t>
         </is>
       </c>
       <c r="B64" s="15" t="n"/>
@@ -3518,8 +3533,20 @@
       <c r="E64" s="15" t="n"/>
       <c r="F64" s="15" t="n"/>
     </row>
-    <row r="65" ht="176" customHeight="1">
+    <row r="65" ht="14" customHeight="1">
       <c r="A65" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="F65" s="17" t="n"/>
+    </row>
+    <row r="66" ht="176" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -3535,20 +3562,20 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="14" t="inlineStr">
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B66" s="15" t="n"/>
-      <c r="C66" s="15" t="n"/>
-      <c r="D66" s="15" t="n"/>
-      <c r="E66" s="15" t="n"/>
-      <c r="F66" s="15" t="n"/>
-    </row>
-    <row r="67" ht="80" customHeight="1">
-      <c r="A67" s="16" t="inlineStr">
+      <c r="B67" s="17" t="n"/>
+      <c r="C67" s="17" t="n"/>
+      <c r="D67" s="17" t="n"/>
+      <c r="E67" s="17" t="n"/>
+      <c r="F67" s="17" t="n"/>
+    </row>
+    <row r="68" ht="80" customHeight="1">
+      <c r="A68" s="18" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95와
@@ -3558,227 +3585,215 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="6" customHeight="1"/>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="69" ht="6" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
         <is>
           <t>릴렉스 샤워코롱    ↗ 원본</t>
         </is>
       </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C71" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D71" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F71" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B71" s="17" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>65g</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
+      <c r="C72" s="20" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="D71" s="19" t="inlineStr">
+      <c r="D72" s="21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E71" s="17" t="inlineStr">
+      <c r="E72" s="19" t="inlineStr">
         <is>
           <t>곡물발효</t>
         </is>
       </c>
-      <c r="F71" s="17" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="17" t="inlineStr">
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr">
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C72" s="18" t="inlineStr">
+      <c r="C73" s="20" t="inlineStr">
         <is>
           <t>17%</t>
         </is>
       </c>
-      <c r="D72" s="22" t="inlineStr">
+      <c r="D73" s="24" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E72" s="17" t="inlineStr">
+      <c r="E73" s="19" t="inlineStr">
         <is>
           <t>진정, 라벤더꽃을 수증기증류추출</t>
         </is>
       </c>
-      <c r="F72" s="17" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>어성초우린물, 캐모마일워터 등</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="48" customHeight="1">
-      <c r="A73" s="17" t="inlineStr">
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>식물성글리세린</t>
         </is>
       </c>
-      <c r="B73" s="17" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C73" s="18" t="inlineStr">
+      <c r="C74" s="20" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D73" s="25" t="inlineStr">
+      <c r="D74" s="27" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E73" s="17" t="inlineStr">
+      <c r="E74" s="19" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F73" s="17" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="17" t="inlineStr">
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>오렌지에센셜오일</t>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B75" s="19" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C74" s="18" t="inlineStr">
+      <c r="C75" s="20" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E74" s="17" t="inlineStr">
+      <c r="E75" s="19" t="inlineStr">
         <is>
           <t>오렌지껍질압착, 달콤한 향</t>
         </is>
       </c>
-      <c r="F74" s="17" t="inlineStr">
+      <c r="F75" s="19" t="inlineStr">
         <is>
           <t>버가못, 레몬EO</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="17" t="inlineStr">
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B75" s="17" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C75" s="18" t="inlineStr">
+      <c r="C76" s="20" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D75" s="11" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E75" s="17" t="inlineStr">
+      <c r="E76" s="19" t="inlineStr">
         <is>
           <t>라벤더꽃에서 추출,진정, 불면증 도움</t>
         </is>
       </c>
-      <c r="F75" s="17" t="inlineStr">
+      <c r="F76" s="19" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 향 2</t>
-        </is>
-      </c>
-      <c r="B76" s="13" t="n"/>
-      <c r="C76" s="13" t="n"/>
-      <c r="D76" s="13" t="n"/>
-      <c r="E76" s="13" t="n"/>
-      <c r="F76" s="13" t="n"/>
     </row>
     <row r="77" ht="14" customHeight="1">
       <c r="A77" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 17 · 보습 6 · 활성 75 · 향 2</t>
         </is>
       </c>
       <c r="B77" s="15" t="n"/>
@@ -3787,8 +3802,20 @@
       <c r="E77" s="15" t="n"/>
       <c r="F77" s="15" t="n"/>
     </row>
-    <row r="78" ht="208" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="n"/>
+      <c r="C78" s="17" t="n"/>
+      <c r="D78" s="17" t="n"/>
+      <c r="E78" s="17" t="n"/>
+      <c r="F78" s="17" t="n"/>
+    </row>
+    <row r="79" ht="208" customHeight="1">
+      <c r="A79" s="22" t="inlineStr">
         <is>
           <t>시중에 판매되는 향수나 샤워코롱에 뭐가 들어가는지도 모르고
 들어가는 향성분이 대부분 합성향이라 신경교란이나 두통 등을 유발한다는데
@@ -3805,26 +3832,26 @@
 '방향제'로도요^^</t>
         </is>
       </c>
-      <c r="B78" s="21" t="n"/>
-      <c r="C78" s="21" t="n"/>
-      <c r="D78" s="21" t="n"/>
-      <c r="E78" s="21" t="n"/>
-      <c r="F78" s="21" t="n"/>
-    </row>
-    <row r="79" ht="14" customHeight="1">
-      <c r="A79" s="14" t="inlineStr">
+      <c r="B79" s="23" t="n"/>
+      <c r="C79" s="23" t="n"/>
+      <c r="D79" s="23" t="n"/>
+      <c r="E79" s="23" t="n"/>
+      <c r="F79" s="23" t="n"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B79" s="15" t="n"/>
-      <c r="C79" s="15" t="n"/>
-      <c r="D79" s="15" t="n"/>
-      <c r="E79" s="15" t="n"/>
-      <c r="F79" s="15" t="n"/>
-    </row>
-    <row r="80" ht="80" customHeight="1">
-      <c r="A80" s="20" t="inlineStr">
+      <c r="B80" s="17" t="n"/>
+      <c r="C80" s="17" t="n"/>
+      <c r="D80" s="17" t="n"/>
+      <c r="E80" s="17" t="n"/>
+      <c r="F80" s="17" t="n"/>
+    </row>
+    <row r="81" ht="80" customHeight="1">
+      <c r="A81" s="22" t="inlineStr">
         <is>
           <t>만들기과정
 1.100ml용기에 아로마베이스95
@@ -3833,129 +3860,117 @@
 4. 흔들어주면 완성.</t>
         </is>
       </c>
-      <c r="B80" s="21" t="n"/>
-      <c r="C80" s="21" t="n"/>
-      <c r="D80" s="21" t="n"/>
-      <c r="E80" s="21" t="n"/>
-      <c r="F80" s="21" t="n"/>
-    </row>
-    <row r="81" ht="6" customHeight="1"/>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="B81" s="23" t="n"/>
+      <c r="C81" s="23" t="n"/>
+      <c r="D81" s="23" t="n"/>
+      <c r="E81" s="23" t="n"/>
+      <c r="F81" s="23" t="n"/>
+    </row>
+    <row r="82" ht="6" customHeight="1"/>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>계피 진드기ZERO 스프레이    [100ml / 용기기준]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="6" t="n"/>
-      <c r="D82" s="6" t="n"/>
-      <c r="E82" s="6" t="n"/>
-      <c r="F82" s="6" t="n"/>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
+      <c r="B83" s="8" t="n"/>
+      <c r="C83" s="8" t="n"/>
+      <c r="D83" s="8" t="n"/>
+      <c r="E83" s="8" t="n"/>
+      <c r="F83" s="8" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B84" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F84" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="304" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="85" ht="304" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>계피에센셜오일 / (시나몬오일)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>40방울 / (2ml)</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D84" s="11" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>녹나무과 식물이고 나무껍질을 주로 활용. / 중국,스리랑카, 인도, 동남아시아가 원산지죠. / 계피 나무껍질 향은 상당히 강하고 달콤하면서 맵습니다. / 계피의 나무껍질을 수증기증류법으로 추출하면몇십배 농축된 계피오일을 추출할 수 있습니다.주성분이 시남알데히드(cinnamaldehyde)로 80~90%을 차지. 알데하이드성분은 벌레퇴치,항진균효과가 탁월. 계피오일은 예로부터 강력한 살균, 항진균, 방충, 소화촉진 마취, 방부효과가 있어 활용한 예가 많습니다. / 단, 고농축인 계피오일은 피부자극이 있기 때문에 피부에 직접 사용하는 것은 피해주세요. / 임산부도 사용을 금합니다.</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n"/>
-    </row>
-    <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="F85" s="10" t="n"/>
+    </row>
+    <row r="86" ht="48" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
       </c>
-      <c r="D85" s="26" t="inlineStr">
+      <c r="D86" s="28" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>보존제, 희석용매, 오일이 분리되지 않고 잘 분산이 되도록 함.</t>
         </is>
       </c>
-      <c r="F85" s="8" t="n"/>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  향 2 · 방부 98</t>
-        </is>
-      </c>
-      <c r="B86" s="13" t="n"/>
-      <c r="C86" s="13" t="n"/>
-      <c r="D86" s="13" t="n"/>
-      <c r="E86" s="13" t="n"/>
-      <c r="F86" s="13" t="n"/>
+      <c r="F86" s="10" t="n"/>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  향 2 · 방부 98</t>
         </is>
       </c>
       <c r="B87" s="15" t="n"/>
@@ -3964,8 +3979,20 @@
       <c r="E87" s="15" t="n"/>
       <c r="F87" s="15" t="n"/>
     </row>
-    <row r="88" ht="384" customHeight="1">
+    <row r="88" ht="14" customHeight="1">
       <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="n"/>
+      <c r="C88" s="17" t="n"/>
+      <c r="D88" s="17" t="n"/>
+      <c r="E88" s="17" t="n"/>
+      <c r="F88" s="17" t="n"/>
+    </row>
+    <row r="89" ht="384" customHeight="1">
+      <c r="A89" s="18" t="inlineStr">
         <is>
           <t>큰아이 다은이는 코막힘, 콧물 증상 때문에 병원에 한번씩 가면
 담당 의사선생님이 감기약보다 알르레기 비염약도 항상 처방을 해주셨어요.
@@ -3994,8 +4021,8 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="384" customHeight="1">
-      <c r="A89" s="16" t="inlineStr">
+    <row r="90" ht="384" customHeight="1">
+      <c r="A90" s="18" t="inlineStr">
         <is>
           <t>어미진드기는 3주마다 새진드기를 낳습니다. 어마어한 놈입니다.ㅠㅠ
 여러 매체에서 소개된 각종 알레르기 질환의 주범인
@@ -4024,8 +4051,8 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="336" customHeight="1">
-      <c r="A90" s="16" t="inlineStr">
+    <row r="91" ht="336" customHeight="1">
+      <c r="A91" s="18" t="inlineStr">
         <is>
           <t>중국, 스리랑카, 인도, 동남아시아가 원산지죠.
 계피 나무껍질,잎의 향은 상당히 강하고 달콤하면서 맵습니다.
@@ -4051,20 +4078,20 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="14" t="inlineStr">
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B91" s="15" t="n"/>
-      <c r="C91" s="15" t="n"/>
-      <c r="D91" s="15" t="n"/>
-      <c r="E91" s="15" t="n"/>
-      <c r="F91" s="15" t="n"/>
-    </row>
-    <row r="92" ht="144" customHeight="1">
-      <c r="A92" s="16" t="inlineStr">
+      <c r="B92" s="17" t="n"/>
+      <c r="C92" s="17" t="n"/>
+      <c r="D92" s="17" t="n"/>
+      <c r="E92" s="17" t="n"/>
+      <c r="F92" s="17" t="n"/>
+    </row>
+    <row r="93" ht="144" customHeight="1">
+      <c r="A93" s="18" t="inlineStr">
         <is>
           <t>계피스프레이 초정밀 만들기과정
 [100ml 용기기준]
@@ -4078,121 +4105,121 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="6" customHeight="1"/>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="94" ht="6" customHeight="1"/>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>어성초팅크처    ↗ 원본</t>
         </is>
       </c>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="6" t="n"/>
-      <c r="D94" s="6" t="n"/>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="6" t="n"/>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="7" t="inlineStr">
+      <c r="B95" s="8" t="n"/>
+      <c r="C95" s="8" t="n"/>
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="8" t="n"/>
+      <c r="F95" s="8" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="B96" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C96" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D96" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E95" s="7" t="inlineStr">
+      <c r="E96" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr">
+      <c r="F96" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="64" customHeight="1">
-      <c r="A96" s="17" t="inlineStr">
+    <row r="97" ht="64" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B96" s="17" t="inlineStr">
+      <c r="B97" s="19" t="inlineStr">
         <is>
           <t>7.41%</t>
         </is>
       </c>
-      <c r="C96" s="18" t="inlineStr"/>
-      <c r="D96" s="19" t="inlineStr">
+      <c r="C97" s="20" t="inlineStr"/>
+      <c r="D97" s="21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E96" s="17" t="inlineStr">
+      <c r="E97" s="19" t="inlineStr">
         <is>
           <t>어성초 추출, 물고기 비린내가 난다하여 어성초, 각종 피부트러블, 피부 개선에 사용</t>
         </is>
       </c>
-      <c r="F96" s="17" t="inlineStr">
+      <c r="F97" s="19" t="inlineStr">
         <is>
           <t>녹차, 병풀, 알란토인,카렌듈라추출물, 유기농 프레쉬 5솔루션 등</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="32" customHeight="1">
-      <c r="A97" s="17" t="inlineStr">
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>에탄올(변성)</t>
         </is>
       </c>
-      <c r="B97" s="17" t="inlineStr">
+      <c r="B98" s="19" t="inlineStr">
         <is>
           <t>92.59%</t>
         </is>
       </c>
-      <c r="C97" s="18" t="inlineStr"/>
-      <c r="D97" s="27" t="inlineStr">
+      <c r="C98" s="20" t="inlineStr"/>
+      <c r="D98" s="29" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E97" s="17" t="inlineStr">
+      <c r="E98" s="19" t="inlineStr">
         <is>
           <t>가용화제, / 물에 오일이 골고루 분산</t>
         </is>
       </c>
-      <c r="F97" s="17" t="inlineStr">
+      <c r="F98" s="19" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="14" t="inlineStr">
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B98" s="15" t="n"/>
-      <c r="C98" s="15" t="n"/>
-      <c r="D98" s="15" t="n"/>
-      <c r="E98" s="15" t="n"/>
-      <c r="F98" s="15" t="n"/>
-    </row>
-    <row r="99" ht="144" customHeight="1">
-      <c r="A99" s="20" t="inlineStr">
+      <c r="B99" s="17" t="n"/>
+      <c r="C99" s="17" t="n"/>
+      <c r="D99" s="17" t="n"/>
+      <c r="E99" s="17" t="n"/>
+      <c r="F99" s="17" t="n"/>
+    </row>
+    <row r="100" ht="144" customHeight="1">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>◎ 이렇게 잘 만들어진 어성초팅크처
 1. 보관기간은 알콜이기 때문에 1년이상 보관하실 수 있구요.
@@ -4201,407 +4228,395 @@
 4. 더 진하게 만들고 싶다면.. 담그고 2주 후 어성초건초를 빼내고 새로운 어성초 40g정도를 넣어주세요. 또 2주나 한달을 숙성하시면 되요. 그러면 한번한 것보다는 팅크처를 진하게 만들 수 있어요. ^^</t>
         </is>
       </c>
-      <c r="B99" s="21" t="n"/>
-      <c r="C99" s="21" t="n"/>
-      <c r="D99" s="21" t="n"/>
-      <c r="E99" s="21" t="n"/>
-      <c r="F99" s="21" t="n"/>
-    </row>
-    <row r="100" ht="14" customHeight="1">
-      <c r="A100" s="14" t="inlineStr">
+      <c r="B100" s="23" t="n"/>
+      <c r="C100" s="23" t="n"/>
+      <c r="D100" s="23" t="n"/>
+      <c r="E100" s="23" t="n"/>
+      <c r="F100" s="23" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B100" s="15" t="n"/>
-      <c r="C100" s="15" t="n"/>
-      <c r="D100" s="15" t="n"/>
-      <c r="E100" s="15" t="n"/>
-      <c r="F100" s="15" t="n"/>
-    </row>
-    <row r="101" ht="48" customHeight="1">
-      <c r="A101" s="20" t="inlineStr">
+      <c r="B101" s="17" t="n"/>
+      <c r="C101" s="17" t="n"/>
+      <c r="D101" s="17" t="n"/>
+      <c r="E101" s="17" t="n"/>
+      <c r="F101" s="17" t="n"/>
+    </row>
+    <row r="102" ht="48" customHeight="1">
+      <c r="A102" s="22" t="inlineStr">
         <is>
           <t>1. 어성초건초 40g을 병에 눌러 담는다.
 2. 병에 식물성에탄올(순수발효주정) 500g 넣는다.
 3. 2주나 한달정도 숙성하면 완성!(그늘지고 서늘한 곳에서 보관요)</t>
         </is>
       </c>
-      <c r="B101" s="21" t="n"/>
-      <c r="C101" s="21" t="n"/>
-      <c r="D101" s="21" t="n"/>
-      <c r="E101" s="21" t="n"/>
-      <c r="F101" s="21" t="n"/>
-    </row>
-    <row r="102" ht="6" customHeight="1"/>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
+      <c r="B102" s="23" t="n"/>
+      <c r="C102" s="23" t="n"/>
+      <c r="D102" s="23" t="n"/>
+      <c r="E102" s="23" t="n"/>
+      <c r="F102" s="23" t="n"/>
+    </row>
+    <row r="103" ht="6" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>아로마 물파스    ↗ 원본</t>
         </is>
       </c>
-      <c r="B103" s="6" t="n"/>
-      <c r="C103" s="6" t="n"/>
-      <c r="D103" s="6" t="n"/>
-      <c r="E103" s="6" t="n"/>
-      <c r="F103" s="6" t="n"/>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="7" t="inlineStr">
+      <c r="B104" s="8" t="n"/>
+      <c r="C104" s="8" t="n"/>
+      <c r="D104" s="8" t="n"/>
+      <c r="E104" s="8" t="n"/>
+      <c r="F104" s="8" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B105" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C105" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D104" s="7" t="inlineStr">
+      <c r="D105" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E105" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr">
+      <c r="F105" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>위치헤이즐워터</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B106" s="10" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C105" s="9" t="inlineStr">
+      <c r="C106" s="11" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="D105" s="22" t="inlineStr">
+      <c r="D106" s="24" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E106" s="10" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="F105" s="8" t="inlineStr">
+      <c r="F106" s="10" t="inlineStr">
         <is>
           <t>편백워터</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="32" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>알로에겔(국내거제산)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C107" s="11" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
-      <c r="D106" s="19" t="inlineStr">
+      <c r="D107" s="21" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E107" s="10" t="inlineStr">
         <is>
           <t>수분공급,진정</t>
         </is>
       </c>
-      <c r="F106" s="8" t="n"/>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="F107" s="10" t="n"/>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C108" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D107" s="23" t="inlineStr">
+      <c r="D108" s="25" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
+      <c r="E108" s="10" t="inlineStr">
         <is>
           <t>점증제</t>
         </is>
       </c>
-      <c r="F107" s="8" t="n"/>
-    </row>
-    <row r="108" ht="64" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="F108" s="10" t="n"/>
+    </row>
+    <row r="109" ht="64" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>멘톨</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C109" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D108" s="22" t="inlineStr">
+      <c r="D109" s="24" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>박하뇌라고도하고 알콜성분, 박하의 잎, 꽃에서 수증기 증류하여 얻어진다. 물에 녹지않고 진통제 가려움증을 멈추는데 사용</t>
         </is>
       </c>
-      <c r="F108" s="8" t="n"/>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="F109" s="10" t="n"/>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>식물성에탄올</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>16g</t>
         </is>
       </c>
-      <c r="C109" s="9" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="D109" s="22" t="inlineStr">
+      <c r="D110" s="24" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
         <is>
           <t>곡물발효주정, 소주원액, 소독</t>
         </is>
       </c>
-      <c r="F109" s="8" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>인플라신</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D110" s="10" t="inlineStr">
+      <c r="D111" s="12" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
+      <c r="E111" s="10" t="inlineStr">
         <is>
           <t>항염</t>
         </is>
       </c>
-      <c r="F110" s="8" t="inlineStr">
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>알란토인</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="32" customHeight="1">
-      <c r="A111" s="8" t="inlineStr">
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="10" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C112" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D111" s="24" t="inlineStr">
+      <c r="D112" s="26" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E111" s="8" t="inlineStr">
+      <c r="E112" s="10" t="inlineStr">
         <is>
           <t>가용화제, 워터와 오일들 분리저지</t>
         </is>
       </c>
-      <c r="F111" s="8" t="inlineStr">
+      <c r="F112" s="10" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="8" t="inlineStr">
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B112" s="8" t="inlineStr">
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C112" s="9" t="inlineStr">
+      <c r="C113" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
+      <c r="D113" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E112" s="8" t="inlineStr">
+      <c r="E113" s="10" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="F112" s="8" t="inlineStr">
+      <c r="F113" s="10" t="inlineStr">
         <is>
           <t>캐모마일로먼,저먼</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="8" t="inlineStr">
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B113" s="8" t="inlineStr">
+      <c r="B114" s="10" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C114" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D113" s="11" t="inlineStr">
+      <c r="D114" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E113" s="8" t="inlineStr">
+      <c r="E114" s="10" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="F113" s="8" t="inlineStr">
+      <c r="F114" s="10" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="32" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+    <row r="115" ht="32" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
         <is>
           <t>로즈마리에센셜오일</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B115" s="10" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C114" s="9" t="inlineStr">
+      <c r="C115" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr">
+      <c r="D115" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E114" s="8" t="inlineStr">
+      <c r="E115" s="10" t="inlineStr">
         <is>
           <t>혈액순환</t>
         </is>
       </c>
-      <c r="F114" s="8" t="inlineStr">
+      <c r="F115" s="10" t="inlineStr">
         <is>
           <t>페파민트 등</t>
         </is>
       </c>
-    </row>
-    <row r="115" ht="14" customHeight="1">
-      <c r="A115" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 67 · 유화 2 · 활성 19 · 향 2 · 점증/pH 1 · 기타 10</t>
-        </is>
-      </c>
-      <c r="B115" s="13" t="n"/>
-      <c r="C115" s="13" t="n"/>
-      <c r="D115" s="13" t="n"/>
-      <c r="E115" s="13" t="n"/>
-      <c r="F115" s="13" t="n"/>
     </row>
     <row r="116" ht="14" customHeight="1">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 67 · 유화 2 · 활성 19 · 향 2 · 점증/pH 1 · 기타 10</t>
         </is>
       </c>
       <c r="B116" s="15" t="n"/>
@@ -4610,8 +4625,20 @@
       <c r="E116" s="15" t="n"/>
       <c r="F116" s="15" t="n"/>
     </row>
-    <row r="117" ht="80" customHeight="1">
+    <row r="117" ht="14" customHeight="1">
       <c r="A117" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="n"/>
+      <c r="C117" s="17" t="n"/>
+      <c r="D117" s="17" t="n"/>
+      <c r="E117" s="17" t="n"/>
+      <c r="F117" s="17" t="n"/>
+    </row>
+    <row r="118" ht="80" customHeight="1">
+      <c r="A118" s="18" t="inlineStr">
         <is>
           <t>[ 레시피 재료 ]
 ① 위치헤이즐워터 50g, 천연알로에베라원액 20g, 하이셀 1g
@@ -4620,20 +4647,20 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="14" customHeight="1">
-      <c r="A118" s="14" t="inlineStr">
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B118" s="15" t="n"/>
-      <c r="C118" s="15" t="n"/>
-      <c r="D118" s="15" t="n"/>
-      <c r="E118" s="15" t="n"/>
-      <c r="F118" s="15" t="n"/>
-    </row>
-    <row r="119" ht="128" customHeight="1">
-      <c r="A119" s="16" t="inlineStr">
+      <c r="B119" s="17" t="n"/>
+      <c r="C119" s="17" t="n"/>
+      <c r="D119" s="17" t="n"/>
+      <c r="E119" s="17" t="n"/>
+      <c r="F119" s="17" t="n"/>
+    </row>
+    <row r="120" ht="128" customHeight="1">
+      <c r="A120" s="18" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 알로에겔, 위치헤이즐워터, 하이셀을 계량한다.
@@ -4646,127 +4673,115 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="6" customHeight="1"/>
-    <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
+    <row r="121" ht="6" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="7" t="inlineStr">
         <is>
           <t>데일리 스마트폰 소독제    [100ml기준]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B121" s="6" t="n"/>
-      <c r="C121" s="6" t="n"/>
-      <c r="D121" s="6" t="n"/>
-      <c r="E121" s="6" t="n"/>
-      <c r="F121" s="6" t="n"/>
-    </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="7" t="inlineStr">
+      <c r="B122" s="8" t="n"/>
+      <c r="C122" s="8" t="n"/>
+      <c r="D122" s="8" t="n"/>
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="8" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B122" s="7" t="inlineStr">
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C122" s="7" t="inlineStr">
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D122" s="7" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E122" s="7" t="inlineStr">
+      <c r="E123" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F122" s="7" t="inlineStr">
+      <c r="F123" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="32" customHeight="1">
-      <c r="A123" s="17" t="inlineStr">
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="19" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
         </is>
       </c>
-      <c r="B123" s="17" t="inlineStr">
+      <c r="B124" s="19" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C123" s="18" t="inlineStr">
+      <c r="C124" s="20" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D124" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E123" s="17" t="inlineStr">
+      <c r="E124" s="19" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼향, 기분전환, / 항균^^</t>
         </is>
       </c>
-      <c r="F123" s="17" t="inlineStr">
+      <c r="F124" s="19" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="17" t="inlineStr">
+    <row r="125" ht="32" customHeight="1">
+      <c r="A125" s="19" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B124" s="17" t="inlineStr">
+      <c r="B125" s="19" t="inlineStr">
         <is>
           <t>100ml(87g)</t>
         </is>
       </c>
-      <c r="C124" s="18" t="inlineStr">
+      <c r="C125" s="20" t="inlineStr">
         <is>
           <t>99%</t>
         </is>
       </c>
-      <c r="D124" s="10" t="inlineStr">
+      <c r="D125" s="12" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E124" s="17" t="inlineStr">
+      <c r="E125" s="19" t="inlineStr">
         <is>
           <t>소독,살균</t>
         </is>
       </c>
-      <c r="F124" s="17" t="n"/>
-    </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  향 1 · 기타 99</t>
-        </is>
-      </c>
-      <c r="B125" s="13" t="n"/>
-      <c r="C125" s="13" t="n"/>
-      <c r="D125" s="13" t="n"/>
-      <c r="E125" s="13" t="n"/>
-      <c r="F125" s="13" t="n"/>
+      <c r="F125" s="19" t="n"/>
     </row>
     <row r="126" ht="14" customHeight="1">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  향 1 · 기타 99</t>
         </is>
       </c>
       <c r="B126" s="15" t="n"/>
@@ -4775,8 +4790,20 @@
       <c r="E126" s="15" t="n"/>
       <c r="F126" s="15" t="n"/>
     </row>
-    <row r="127" ht="384" customHeight="1">
-      <c r="A127" s="20" t="inlineStr">
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="n"/>
+      <c r="C127" s="17" t="n"/>
+      <c r="D127" s="17" t="n"/>
+      <c r="E127" s="17" t="n"/>
+      <c r="F127" s="17" t="n"/>
+    </row>
+    <row r="128" ht="384" customHeight="1">
+      <c r="A128" s="22" t="inlineStr">
         <is>
           <t>매일 사용하는 스마트폰이 화장실변기보다 세균과 바이러스가 10배이상 많이 검출된다는
 뉴스를 접한 적이 있어요. (뜨아~~)
@@ -4804,14 +4831,14 @@
 이 막은 에탄올이 세균 내부로 침투하는 것을 막습니다.</t>
         </is>
       </c>
-      <c r="B127" s="21" t="n"/>
-      <c r="C127" s="21" t="n"/>
-      <c r="D127" s="21" t="n"/>
-      <c r="E127" s="21" t="n"/>
-      <c r="F127" s="21" t="n"/>
-    </row>
-    <row r="128" ht="384" customHeight="1">
-      <c r="A128" s="20" t="inlineStr">
+      <c r="B128" s="23" t="n"/>
+      <c r="C128" s="23" t="n"/>
+      <c r="D128" s="23" t="n"/>
+      <c r="E128" s="23" t="n"/>
+      <c r="F128" s="23" t="n"/>
+    </row>
+    <row r="129" ht="384" customHeight="1">
+      <c r="A129" s="22" t="inlineStr">
         <is>
           <t>따라서 살균작용이 효과적으로 일어나게 하려면 순수 에탄올에 물을 섞어야 한답니다.
 세균 표면의 막을 한꺼번에 응고시키는 것을 막아고
@@ -4839,39 +4866,39 @@
 방법은 같습니다.</t>
         </is>
       </c>
-      <c r="B128" s="21" t="n"/>
-      <c r="C128" s="21" t="n"/>
-      <c r="D128" s="21" t="n"/>
-      <c r="E128" s="21" t="n"/>
-      <c r="F128" s="21" t="n"/>
-    </row>
-    <row r="129" ht="32" customHeight="1">
-      <c r="A129" s="20" t="inlineStr">
+      <c r="B129" s="23" t="n"/>
+      <c r="C129" s="23" t="n"/>
+      <c r="D129" s="23" t="n"/>
+      <c r="E129" s="23" t="n"/>
+      <c r="F129" s="23" t="n"/>
+    </row>
+    <row r="130" ht="32" customHeight="1">
+      <c r="A130" s="22" t="inlineStr">
         <is>
           <t>면거즈나 (키친타올이나) 티슈에 촉촉할 정도로 적셔서
 닦아주세요.</t>
         </is>
       </c>
-      <c r="B129" s="21" t="n"/>
-      <c r="C129" s="21" t="n"/>
-      <c r="D129" s="21" t="n"/>
-      <c r="E129" s="21" t="n"/>
-      <c r="F129" s="21" t="n"/>
-    </row>
-    <row r="130" ht="14" customHeight="1">
-      <c r="A130" s="14" t="inlineStr">
+      <c r="B130" s="23" t="n"/>
+      <c r="C130" s="23" t="n"/>
+      <c r="D130" s="23" t="n"/>
+      <c r="E130" s="23" t="n"/>
+      <c r="F130" s="23" t="n"/>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B130" s="15" t="n"/>
-      <c r="C130" s="15" t="n"/>
-      <c r="D130" s="15" t="n"/>
-      <c r="E130" s="15" t="n"/>
-      <c r="F130" s="15" t="n"/>
-    </row>
-    <row r="131" ht="208" customHeight="1">
-      <c r="A131" s="20" t="inlineStr">
+      <c r="B131" s="17" t="n"/>
+      <c r="C131" s="17" t="n"/>
+      <c r="D131" s="17" t="n"/>
+      <c r="E131" s="17" t="n"/>
+      <c r="F131" s="17" t="n"/>
+    </row>
+    <row r="132" ht="208" customHeight="1">
+      <c r="A132" s="22" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.용기에 에센셜오일을 20방울 떨어뜨려주세요. (에센셜오일을 넣지 않는다면 생략 가능)
@@ -4887,165 +4914,153 @@
 오랜만에 닦으니 어찌나 지저분한지.. 상큼한 레몬 잔향이 기분좋게 만드네요.</t>
         </is>
       </c>
-      <c r="B131" s="21" t="n"/>
-      <c r="C131" s="21" t="n"/>
-      <c r="D131" s="21" t="n"/>
-      <c r="E131" s="21" t="n"/>
-      <c r="F131" s="21" t="n"/>
-    </row>
-    <row r="132" ht="6" customHeight="1"/>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
+      <c r="B132" s="23" t="n"/>
+      <c r="C132" s="23" t="n"/>
+      <c r="D132" s="23" t="n"/>
+      <c r="E132" s="23" t="n"/>
+      <c r="F132" s="23" t="n"/>
+    </row>
+    <row r="133" ht="6" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>아로마 손소독제스프레이    ↗ 원본</t>
         </is>
       </c>
-      <c r="B133" s="6" t="n"/>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6" t="n"/>
-      <c r="E133" s="6" t="n"/>
-      <c r="F133" s="6" t="n"/>
-    </row>
-    <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
+      <c r="B134" s="8" t="n"/>
+      <c r="C134" s="8" t="n"/>
+      <c r="D134" s="8" t="n"/>
+      <c r="E134" s="8" t="n"/>
+      <c r="F134" s="8" t="n"/>
+    </row>
+    <row r="135" ht="15" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B135" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C134" s="7" t="inlineStr">
+      <c r="C135" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D134" s="7" t="inlineStr">
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E134" s="7" t="inlineStr">
+      <c r="E135" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F134" s="7" t="inlineStr">
+      <c r="F135" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="64" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="136" ht="64" customHeight="1">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>465ml</t>
         </is>
       </c>
-      <c r="C135" s="9" t="inlineStr">
+      <c r="C136" s="11" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr">
+      <c r="D136" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E135" s="8" t="inlineStr">
+      <c r="E136" s="10" t="inlineStr">
         <is>
           <t>곡물 발효 , / 소독효과가 제일 좋은 70% 알코올함량, / 에센셜오일 분산, 방향용으로 사용시 / 공기정화, 소독효과.</t>
         </is>
       </c>
-      <c r="F135" s="8" t="n"/>
-    </row>
-    <row r="136" ht="48" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="F136" s="10" t="n"/>
+    </row>
+    <row r="137" ht="48" customHeight="1">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>22.5g</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr">
+      <c r="C137" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D136" s="25" t="inlineStr">
+      <c r="D137" s="27" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E136" s="8" t="inlineStr">
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t>손 보습제, 향과 알코올이 오랫동안 머물 수 / 있도록 고착제 역할을 함.</t>
         </is>
       </c>
-      <c r="F136" s="8" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="48" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+    <row r="138" ht="48" customHeight="1">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>(레몬) 에센셜오일</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>2~5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D138" s="13" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E137" s="8" t="inlineStr">
+      <c r="E138" s="10" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 / 천연오일. 원하는 향.</t>
         </is>
       </c>
-      <c r="F137" s="8" t="inlineStr">
+      <c r="F138" s="10" t="inlineStr">
         <is>
           <t>클린코튼, 그린티시트러스, 체리블라썸 향 등</t>
         </is>
       </c>
-    </row>
-    <row r="138" ht="14" customHeight="1">
-      <c r="A138" s="12" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  보습 5 · 향 95</t>
-        </is>
-      </c>
-      <c r="B138" s="13" t="n"/>
-      <c r="C138" s="13" t="n"/>
-      <c r="D138" s="13" t="n"/>
-      <c r="E138" s="13" t="n"/>
-      <c r="F138" s="13" t="n"/>
     </row>
     <row r="139" ht="14" customHeight="1">
       <c r="A139" s="14" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  보습 5 · 향 95</t>
         </is>
       </c>
       <c r="B139" s="15" t="n"/>
@@ -5054,8 +5069,20 @@
       <c r="E139" s="15" t="n"/>
       <c r="F139" s="15" t="n"/>
     </row>
-    <row r="140" ht="384" customHeight="1">
+    <row r="140" ht="14" customHeight="1">
       <c r="A140" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B140" s="17" t="n"/>
+      <c r="C140" s="17" t="n"/>
+      <c r="D140" s="17" t="n"/>
+      <c r="E140" s="17" t="n"/>
+      <c r="F140" s="17" t="n"/>
+    </row>
+    <row r="141" ht="384" customHeight="1">
+      <c r="A141" s="18" t="inlineStr">
         <is>
           <t>2009년 신종 플루 때 안내해드린 레시피입니다.
 이번 메르스, 신종 플루 때처럼 사람들을 불안하게 하네요.
@@ -5084,8 +5111,8 @@
         </is>
       </c>
     </row>
-    <row r="141" ht="96" customHeight="1">
-      <c r="A141" s="16" t="inlineStr">
+    <row r="142" ht="96" customHeight="1">
+      <c r="A142" s="18" t="inlineStr">
         <is>
           <t>에탄올 80%이상에서 살균분무시 알콜성분이 빨리 공기 중에
 증발하여 지속적인 살균이 어렵기도 하답니다.
@@ -5096,20 +5123,20 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="14" t="inlineStr">
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B142" s="15" t="n"/>
-      <c r="C142" s="15" t="n"/>
-      <c r="D142" s="15" t="n"/>
-      <c r="E142" s="15" t="n"/>
-      <c r="F142" s="15" t="n"/>
-    </row>
-    <row r="143" ht="160" customHeight="1">
-      <c r="A143" s="16" t="inlineStr">
+      <c r="B143" s="17" t="n"/>
+      <c r="C143" s="17" t="n"/>
+      <c r="D143" s="17" t="n"/>
+      <c r="E143" s="17" t="n"/>
+      <c r="F143" s="17" t="n"/>
+    </row>
+    <row r="144" ht="160" customHeight="1">
+      <c r="A144" s="18" t="inlineStr">
         <is>
           <t>초간단 만들기과정
 1. 아로마베이스70 속/겉뚜껑을 열고
@@ -5123,10 +5150,11 @@
         </is>
       </c>
     </row>
-    <row r="144" ht="6" customHeight="1"/>
+    <row r="145" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="73">
+  <mergeCells count="74">
     <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A99:F99"/>
     <mergeCell ref="A90:F90"/>
@@ -5134,84 +5162,84 @@
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A118:F118"/>
-    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A120:F120"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A104:F104"/>
     <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A95:F95"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A116:F116"/>
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A141:F141"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A144:F144"/>
     <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A122:F122"/>
     <mergeCell ref="A53:F53"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A134:F134"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A65:F65"/>
     <mergeCell ref="A52:F52"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A9:F9"/>
     <mergeCell ref="A67:F67"/>
     <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A127:F127"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="A92:F92"/>
     <mergeCell ref="A130:F130"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A15:F15"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A142:F142"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A98:F98"/>
-    <mergeCell ref="A138:F138"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A70:F70"/>
     <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A88:F88"/>
     <mergeCell ref="A119:F119"/>
-    <mergeCell ref="A88:F88"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>

--- a/카드_아키타입/00_기타(미분류).xlsx
+++ b/카드_아키타입/00_기타(미분류).xlsx
@@ -652,7 +652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="16014700"/>
+    <pos x="7848600" y="15811500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -672,7 +672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="16014700"/>
+    <pos x="9696450" y="15811500"/>
     <ext cx="1809750" cy="1266825"/>
     <pic>
       <nvPicPr>
@@ -692,7 +692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="16014700"/>
+    <pos x="11544300" y="15811500"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -712,7 +712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="16014700"/>
+    <pos x="13392150" y="15811500"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -732,7 +732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="17862550"/>
+    <pos x="7848600" y="17659350"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -752,7 +752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="17862550"/>
+    <pos x="9696450" y="17659350"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -772,7 +772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="17862550"/>
+    <pos x="11544300" y="17659350"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -792,7 +792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="17862550"/>
+    <pos x="13392150" y="17659350"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -812,7 +812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="19710399"/>
+    <pos x="7848600" y="19507200"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -832,7 +832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="19710399"/>
+    <pos x="9696450" y="19507200"/>
     <ext cx="1809750" cy="1590675"/>
     <pic>
       <nvPicPr>
@@ -852,7 +852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="25831800"/>
+    <pos x="7848600" y="25628600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -872,7 +872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="25831800"/>
+    <pos x="9696450" y="25628600"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -892,7 +892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="25831800"/>
+    <pos x="11544300" y="25628600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -912,7 +912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="25831800"/>
+    <pos x="13392150" y="25628600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -932,7 +932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="27679650"/>
+    <pos x="7848600" y="27476450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -952,7 +952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="27679650"/>
+    <pos x="9696450" y="27476450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -972,7 +972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="32397700"/>
+    <pos x="7848600" y="32194500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -992,7 +992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="32397700"/>
+    <pos x="9696450" y="32194500"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1012,7 +1012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="32397700"/>
+    <pos x="11544300" y="32194500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1032,7 +1032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="32397700"/>
+    <pos x="13392150" y="32194500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1052,7 +1052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="34245550"/>
+    <pos x="7848600" y="34042350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1072,7 +1072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="34245550"/>
+    <pos x="9696450" y="34042350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1092,7 +1092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="38557200"/>
+    <pos x="7848600" y="38354000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1112,7 +1112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="38557200"/>
+    <pos x="9696450" y="38354000"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1132,7 +1132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="38557200"/>
+    <pos x="11544300" y="38354000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1152,7 +1152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="38557200"/>
+    <pos x="13392150" y="38354000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1172,7 +1172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="40405050"/>
+    <pos x="7848600" y="40201849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1192,7 +1192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="40405050"/>
+    <pos x="9696450" y="40201849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1212,7 +1212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="45123100"/>
+    <pos x="7848600" y="44919900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1232,7 +1232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="45123100"/>
+    <pos x="9696450" y="44919900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1252,7 +1252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="45123100"/>
+    <pos x="11544300" y="44919900"/>
     <ext cx="1809750" cy="1057275"/>
     <pic>
       <nvPicPr>
@@ -1272,7 +1272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="45123100"/>
+    <pos x="13392150" y="44919900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1292,7 +1292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="46970950"/>
+    <pos x="7848600" y="46767750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1312,7 +1312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="46970950"/>
+    <pos x="9696450" y="46767750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1332,7 +1332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="46970950"/>
+    <pos x="11544300" y="46767750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1352,7 +1352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="46970950"/>
+    <pos x="13392150" y="46767750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1372,7 +1372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="48818800"/>
+    <pos x="7848600" y="48615600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1392,7 +1392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="48818800"/>
+    <pos x="9696450" y="48615600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1412,7 +1412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="48818800"/>
+    <pos x="11544300" y="48615600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1432,7 +1432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="66522600"/>
+    <pos x="7848600" y="66319400"/>
     <ext cx="1171575" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1452,7 +1452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="71081900"/>
+    <pos x="7848600" y="70878700"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1472,7 +1472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="71081900"/>
+    <pos x="9696450" y="70878700"/>
     <ext cx="1809750" cy="1133475"/>
     <pic>
       <nvPicPr>
@@ -1492,7 +1492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="71081900"/>
+    <pos x="11544300" y="70878700"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1512,7 +1512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78054200"/>
+    <pos x="7848600" y="77851000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1532,7 +1532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="78054200"/>
+    <pos x="9696450" y="77851000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1552,7 +1552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="78054200"/>
+    <pos x="11544300" y="77851000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1572,7 +1572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="78054200"/>
+    <pos x="13392150" y="77851000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1592,7 +1592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="79902050"/>
+    <pos x="7848600" y="79698849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1612,7 +1612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="79902050"/>
+    <pos x="9696450" y="79698849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1632,7 +1632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="79902050"/>
+    <pos x="11544300" y="79698849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1652,7 +1652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="79902050"/>
+    <pos x="13392150" y="79698849"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1672,7 +1672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="81749900"/>
+    <pos x="7848600" y="81546699"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1692,7 +1692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="81749900"/>
+    <pos x="9696450" y="81546699"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1712,7 +1712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="81749900"/>
+    <pos x="11544300" y="81546699"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1732,7 +1732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="92748100"/>
+    <pos x="7848600" y="92544900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1752,7 +1752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="92748100"/>
+    <pos x="9696450" y="92544900"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1772,7 +1772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="92748100"/>
+    <pos x="11544300" y="92544900"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1792,7 +1792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="92748100"/>
+    <pos x="13392150" y="92544900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1812,7 +1812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="94595950"/>
+    <pos x="7848600" y="94392750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1832,7 +1832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="94595950"/>
+    <pos x="9696450" y="94392750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1852,7 +1852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="94595950"/>
+    <pos x="11544300" y="94392750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1872,7 +1872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="94595950"/>
+    <pos x="13392150" y="94392750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1892,7 +1892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="96443800"/>
+    <pos x="7848600" y="96240600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2333,10 +2333,10 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>강,바다에 있는 소금(미네럴)일종. / 연마, 중화, 탈취 등등의 효과. / 약알카리</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="n"/>
+          <t>강,바다에 있는 소금(미네럴)일종. · 연마, 중화, 탈취 등등의 효과. · 약알카리</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일.</t>
+          <t>원하는 · 에센셜오일.</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
+    <row r="18" ht="16" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
           <t>아로마베이스70</t>
@@ -2509,10 +2509,10 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>살균, 소독, / 멘톨 녹이는 용도</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="n"/>
+          <t>살균, 소독 · 멘톨 녹이는 용도</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr"/>
     </row>
     <row r="19" ht="48" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
@@ -2537,10 +2537,10 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>민트류의 화한 휘발성 성분. / 36개월 이하 어린이와 임산부는 빼고 만들어주세요.</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="n"/>
+          <t>민트류의 화한 휘발성 성분. · 36개월 이하 어린이와 임산부는 빼고 만들어주세요.</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr"/>
     </row>
     <row r="20" ht="48" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
@@ -2568,7 +2568,7 @@
           <t>피부트러블에 좋은 8종 약재 호호바, 해바라기오일 등에 담궈 유효성분 우려냄.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="n"/>
+      <c r="F20" s="19" t="inlineStr"/>
     </row>
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F31" s="10" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
           <t>내추럴 셀룰로오즈</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n"/>
+      <c r="F33" s="10" t="inlineStr"/>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -2874,7 +2874,7 @@
           <t>민트의 알콜성분.</t>
         </is>
       </c>
-      <c r="F34" s="10" t="n"/>
+      <c r="F34" s="10" t="inlineStr"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
@@ -2934,7 +2934,7 @@
           <t>민감,진정</t>
         </is>
       </c>
-      <c r="F36" s="10" t="n"/>
+      <c r="F36" s="10" t="inlineStr"/>
     </row>
     <row r="37" ht="64" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -3934,10 +3934,10 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>녹나무과 식물이고 나무껍질을 주로 활용. / 중국,스리랑카, 인도, 동남아시아가 원산지죠. / 계피 나무껍질 향은 상당히 강하고 달콤하면서 맵습니다. / 계피의 나무껍질을 수증기증류법으로 추출하면몇십배 농축된 계피오일을 추출할 수 있습니다.주성분이 시남알데히드(cinnamaldehyde)로 80~90%을 차지. 알데하이드성분은 벌레퇴치,항진균효과가 탁월. 계피오일은 예로부터 강력한 살균, 항진균, 방충, 소화촉진 마취, 방부효과가 있어 활용한 예가 많습니다. / 단, 고농축인 계피오일은 피부자극이 있기 때문에 피부에 직접 사용하는 것은 피해주세요. / 임산부도 사용을 금합니다.</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="n"/>
+          <t>녹나무과 식물이고 나무껍질을 주로 활용. · 중국,스리랑카, 인도, 동남아시아가 원산지죠. · 계피 나무껍질 향은 상당히 강하고 달콤하면서 맵습니다. · 계피의 나무껍질을 수증기증류법으로 추출하면몇십배 농축된 계피오일을 추출할 수 있습니다.주성분이 시남알데히드(cinnamaldehyde)로 80~90%을 차지. 알데하이드성분은 벌레퇴치,항진균효과가 탁월. 계피오일은 예로부터 강력한 살균, 항진균, 방충, 소화촉진 마취, 방부효과가 있어 활용한 예가 많습니다. · 단, 고농축인 계피오일은 피부자극이 있기 때문에 피부에 직접 사용하는 것은 피해주세요. · 임산부도 사용을 금합니다.</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr"/>
     </row>
     <row r="86" ht="48" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
@@ -3965,7 +3965,7 @@
           <t>보존제, 희석용매, 오일이 분리되지 않고 잘 분산이 되도록 함.</t>
         </is>
       </c>
-      <c r="F86" s="10" t="n"/>
+      <c r="F86" s="10" t="inlineStr"/>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="14" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E98" s="19" t="inlineStr">
         <is>
-          <t>가용화제, / 물에 오일이 골고루 분산</t>
+          <t>가용화제 · 물에 오일이 골고루 분산</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
@@ -4363,7 +4363,7 @@
           <t>수분공급,진정</t>
         </is>
       </c>
-      <c r="F107" s="10" t="n"/>
+      <c r="F107" s="10" t="inlineStr"/>
     </row>
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
@@ -4391,7 +4391,7 @@
           <t>점증제</t>
         </is>
       </c>
-      <c r="F108" s="10" t="n"/>
+      <c r="F108" s="10" t="inlineStr"/>
     </row>
     <row r="109" ht="64" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
@@ -4419,7 +4419,7 @@
           <t>박하뇌라고도하고 알콜성분, 박하의 잎, 꽃에서 수증기 증류하여 얻어진다. 물에 녹지않고 진통제 가려움증을 멈추는데 사용</t>
         </is>
       </c>
-      <c r="F109" s="10" t="n"/>
+      <c r="F109" s="10" t="inlineStr"/>
     </row>
     <row r="110" ht="16" customHeight="1">
       <c r="A110" s="10" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="E124" s="19" t="inlineStr">
         <is>
-          <t>레몬껍질오일, 상큼향, 기분전환, / 항균^^</t>
+          <t>레몬껍질오일, 상큼향, 기분전환 · 항균^^</t>
         </is>
       </c>
       <c r="F124" s="19" t="inlineStr">
@@ -4776,7 +4776,7 @@
           <t>소독,살균</t>
         </is>
       </c>
-      <c r="F125" s="19" t="n"/>
+      <c r="F125" s="19" t="inlineStr"/>
     </row>
     <row r="126" ht="14" customHeight="1">
       <c r="A126" s="14" t="inlineStr">
@@ -4988,10 +4988,10 @@
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>곡물 발효 , / 소독효과가 제일 좋은 70% 알코올함량, / 에센셜오일 분산, 방향용으로 사용시 / 공기정화, 소독효과.</t>
-        </is>
-      </c>
-      <c r="F136" s="10" t="n"/>
+          <t>곡물 발효 · 소독효과가 제일 좋은 70% 알코올함량 · 에센셜오일 분산, 방향용으로 사용시 · 공기정화, 소독효과.</t>
+        </is>
+      </c>
+      <c r="F136" s="10" t="inlineStr"/>
     </row>
     <row r="137" ht="48" customHeight="1">
       <c r="A137" s="10" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="E137" s="10" t="inlineStr">
         <is>
-          <t>손 보습제, 향과 알코올이 오랫동안 머물 수 / 있도록 고착제 역할을 함.</t>
+          <t>손 보습제, 향과 알코올이 오랫동안 머물 수 · 있도록 고착제 역할을 함.</t>
         </is>
       </c>
       <c r="F137" s="10" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>레몬껍질에서 추출한 / 천연오일. 원하는 향.</t>
+          <t>레몬껍질에서 추출한 · 천연오일. 원하는 향.</t>
         </is>
       </c>
       <c r="F138" s="10" t="inlineStr">
